--- a/DetalleXDocente20241.xlsx
+++ b/DetalleXDocente20241.xlsx
@@ -948,7 +948,7 @@
         <v>105</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>23</v>
@@ -957,19 +957,19 @@
         <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>92</v>
+        <v>79.3</v>
       </c>
       <c r="H5" s="1">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="I5" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -983,10 +983,10 @@
         <v>105</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1015,28 +1015,28 @@
         <v>106</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>95.5</v>
+        <v>92.5</v>
       </c>
       <c r="H7" s="1">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I7" s="2">
         <v>8.9</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1721,7 +1721,7 @@
         <v>16.2</v>
       </c>
       <c r="I27" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1756,7 +1756,7 @@
         <v>30.3</v>
       </c>
       <c r="I28" s="2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         <v>121</v>
       </c>
       <c r="D31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E31">
         <v>22</v>
@@ -1855,19 +1855,19 @@
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>95.7</v>
+        <v>91.7</v>
       </c>
       <c r="H31" s="1">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I31" s="2">
         <v>9</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1878,7 +1878,7 @@
         <v>106</v>
       </c>
       <c r="D32">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32">
         <v>129</v>
@@ -1887,19 +1887,19 @@
         <v>20</v>
       </c>
       <c r="G32" s="1">
-        <v>86.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="H32" s="1">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="I32" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1913,7 +1913,7 @@
         <v>105</v>
       </c>
       <c r="D33">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E33">
         <v>25</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -1931,10 +1931,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1945,7 +1945,7 @@
         <v>106</v>
       </c>
       <c r="D34">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E34">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -1963,10 +1963,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2566,16 +2566,16 @@
         <v>40</v>
       </c>
       <c r="E52">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F52">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G52" s="1">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="H52" s="1">
-        <v>35</v>
+        <v>32.5</v>
       </c>
       <c r="I52" s="2">
         <v>6.2</v>
@@ -2636,19 +2636,19 @@
         <v>33</v>
       </c>
       <c r="E54">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F54">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G54" s="1">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="H54" s="1">
-        <v>54.5</v>
+        <v>51.5</v>
       </c>
       <c r="I54" s="2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>52.2</v>
       </c>
       <c r="I55" s="2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -2773,16 +2773,16 @@
         <v>170</v>
       </c>
       <c r="E58">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F58">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G58" s="1">
-        <v>58.2</v>
+        <v>59.4</v>
       </c>
       <c r="H58" s="1">
-        <v>41.8</v>
+        <v>40.6</v>
       </c>
       <c r="I58" s="2">
         <v>6.2</v>
@@ -3780,22 +3780,22 @@
         <v>121</v>
       </c>
       <c r="D95">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E95">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F95">
         <v>6</v>
       </c>
       <c r="G95" s="1">
-        <v>73.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H95" s="1">
-        <v>26.1</v>
+        <v>25</v>
       </c>
       <c r="I95" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -3812,19 +3812,19 @@
         <v>106</v>
       </c>
       <c r="D96">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E96">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F96">
         <v>27</v>
       </c>
       <c r="G96" s="1">
-        <v>75</v>
+        <v>75.2</v>
       </c>
       <c r="H96" s="1">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="I96" s="2">
         <v>7</v>
@@ -4089,7 +4089,7 @@
         <v>131</v>
       </c>
       <c r="D104">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E104">
         <v>23</v>
@@ -4098,19 +4098,19 @@
         <v>5</v>
       </c>
       <c r="G104" s="1">
-        <v>82.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="H104" s="1">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="I104" s="2">
         <v>7.8</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4194,7 +4194,7 @@
         <v>132</v>
       </c>
       <c r="D107">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E107">
         <v>35</v>
@@ -4203,19 +4203,19 @@
         <v>5</v>
       </c>
       <c r="G107" s="1">
-        <v>87.5</v>
+        <v>79.5</v>
       </c>
       <c r="H107" s="1">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
       <c r="I107" s="2">
         <v>7.8</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K107" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -4299,7 +4299,7 @@
         <v>121</v>
       </c>
       <c r="D110">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E110">
         <v>23</v>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -4317,10 +4317,10 @@
         <v>8.5</v>
       </c>
       <c r="J110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4331,7 +4331,7 @@
         <v>106</v>
       </c>
       <c r="D111">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E111">
         <v>216</v>
@@ -4340,19 +4340,19 @@
         <v>17</v>
       </c>
       <c r="G111" s="1">
-        <v>92.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H111" s="1">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I111" s="2">
         <v>8.1</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K111" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4885,7 +4885,7 @@
         <v>131</v>
       </c>
       <c r="D127">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E127">
         <v>25</v>
@@ -4894,19 +4894,19 @@
         <v>3</v>
       </c>
       <c r="G127" s="1">
-        <v>89.3</v>
+        <v>86.2</v>
       </c>
       <c r="H127" s="1">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="I127" s="2">
         <v>7.9</v>
       </c>
       <c r="J127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -4920,22 +4920,22 @@
         <v>131</v>
       </c>
       <c r="D128">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E128">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F128">
         <v>3</v>
       </c>
       <c r="G128" s="1">
-        <v>89.3</v>
+        <v>89.7</v>
       </c>
       <c r="H128" s="1">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="I128" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -5092,28 +5092,28 @@
         <v>106</v>
       </c>
       <c r="D133">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E133">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F133">
         <v>53</v>
       </c>
       <c r="G133" s="1">
-        <v>79.5</v>
+        <v>79.2</v>
       </c>
       <c r="H133" s="1">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="I133" s="2">
         <v>7.7</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" s="1">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5142,7 +5142,7 @@
         <v>12.2</v>
       </c>
       <c r="I134" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -5174,7 +5174,7 @@
         <v>12.2</v>
       </c>
       <c r="I135" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -5264,7 +5264,7 @@
         <v>131</v>
       </c>
       <c r="D138">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E138">
         <v>26</v>
@@ -5273,19 +5273,19 @@
         <v>2</v>
       </c>
       <c r="G138" s="1">
-        <v>92.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="H138" s="1">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="I138" s="2">
         <v>8</v>
       </c>
       <c r="J138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K138" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -5299,7 +5299,7 @@
         <v>135</v>
       </c>
       <c r="D139">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E139">
         <v>20</v>
@@ -5308,19 +5308,19 @@
         <v>1</v>
       </c>
       <c r="G139" s="1">
-        <v>95.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H139" s="1">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I139" s="2">
         <v>7.8</v>
       </c>
       <c r="J139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K139" s="1">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -5366,7 +5366,7 @@
         <v>106</v>
       </c>
       <c r="D141">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E141">
         <v>117</v>
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="G141" s="1">
-        <v>93.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H141" s="1">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="I141" s="2">
         <v>7.7</v>
       </c>
       <c r="J141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K141" s="1">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -5713,7 +5713,7 @@
         <v>121</v>
       </c>
       <c r="D151">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E151">
         <v>22</v>
@@ -5722,19 +5722,19 @@
         <v>1</v>
       </c>
       <c r="G151" s="1">
-        <v>95.7</v>
+        <v>91.7</v>
       </c>
       <c r="H151" s="1">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I151" s="2">
         <v>8.5</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -5745,7 +5745,7 @@
         <v>106</v>
       </c>
       <c r="D152">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E152">
         <v>73</v>
@@ -5754,19 +5754,19 @@
         <v>11</v>
       </c>
       <c r="G152" s="1">
-        <v>86.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H152" s="1">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="I152" s="2">
         <v>7.6</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -5952,7 +5952,7 @@
         <v>131</v>
       </c>
       <c r="D158">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E158">
         <v>19</v>
@@ -5961,19 +5961,19 @@
         <v>9</v>
       </c>
       <c r="G158" s="1">
-        <v>67.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="H158" s="1">
-        <v>32.1</v>
+        <v>31</v>
       </c>
       <c r="I158" s="2">
         <v>6.9</v>
       </c>
       <c r="J158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6057,7 +6057,7 @@
         <v>132</v>
       </c>
       <c r="D161">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E161">
         <v>27</v>
@@ -6066,19 +6066,19 @@
         <v>13</v>
       </c>
       <c r="G161" s="1">
-        <v>67.5</v>
+        <v>61.4</v>
       </c>
       <c r="H161" s="1">
-        <v>32.5</v>
+        <v>29.5</v>
       </c>
       <c r="I161" s="2">
         <v>6.6</v>
       </c>
       <c r="J161">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K161" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -6159,7 +6159,7 @@
         <v>106</v>
       </c>
       <c r="D164">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E164">
         <v>159</v>
@@ -6168,19 +6168,19 @@
         <v>51</v>
       </c>
       <c r="G164" s="1">
-        <v>75.7</v>
+        <v>74</v>
       </c>
       <c r="H164" s="1">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
       <c r="I164" s="2">
         <v>6.9</v>
       </c>
       <c r="J164">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K164" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -6264,10 +6264,10 @@
         <v>132</v>
       </c>
       <c r="D167">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E167">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -6299,10 +6299,10 @@
         <v>132</v>
       </c>
       <c r="D168">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E168">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F168">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>0</v>
       </c>
       <c r="I168" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -6331,19 +6331,19 @@
         <v>106</v>
       </c>
       <c r="D169">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E169">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F169">
         <v>2</v>
       </c>
       <c r="G169" s="1">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H169" s="1">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I169" s="2">
         <v>7.4</v>
@@ -6433,7 +6433,7 @@
         <v>135</v>
       </c>
       <c r="D172">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E172">
         <v>10</v>
@@ -6442,19 +6442,19 @@
         <v>10</v>
       </c>
       <c r="G172" s="1">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="H172" s="1">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="I172" s="2">
         <v>6</v>
       </c>
       <c r="J172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -6468,7 +6468,7 @@
         <v>135</v>
       </c>
       <c r="D173">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E173">
         <v>8</v>
@@ -6477,19 +6477,19 @@
         <v>12</v>
       </c>
       <c r="G173" s="1">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="H173" s="1">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="I173" s="2">
         <v>5.3</v>
       </c>
       <c r="J173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K173" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -6573,7 +6573,7 @@
         <v>121</v>
       </c>
       <c r="D176">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E176">
         <v>23</v>
@@ -6582,7 +6582,7 @@
         <v>0</v>
       </c>
       <c r="G176" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
@@ -6591,10 +6591,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K176" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -6608,7 +6608,7 @@
         <v>105</v>
       </c>
       <c r="D177">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E177">
         <v>22</v>
@@ -6617,19 +6617,19 @@
         <v>3</v>
       </c>
       <c r="G177" s="1">
-        <v>88</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H177" s="1">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="I177" s="2">
         <v>7.2</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K177" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -6643,7 +6643,7 @@
         <v>105</v>
       </c>
       <c r="D178">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E178">
         <v>16</v>
@@ -6652,19 +6652,19 @@
         <v>9</v>
       </c>
       <c r="G178" s="1">
-        <v>64</v>
+        <v>55.2</v>
       </c>
       <c r="H178" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I178" s="2">
         <v>6.1</v>
       </c>
       <c r="J178">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K178" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -6675,7 +6675,7 @@
         <v>106</v>
       </c>
       <c r="D179">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E179">
         <v>100</v>
@@ -6684,19 +6684,19 @@
         <v>49</v>
       </c>
       <c r="G179" s="1">
-        <v>67.09999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="H179" s="1">
-        <v>32.9</v>
+        <v>30.6</v>
       </c>
       <c r="I179" s="2">
         <v>6.5</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K179" s="1">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -7853,10 +7853,10 @@
         <v>132</v>
       </c>
       <c r="D213">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E213">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="I213" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J213">
         <v>0</v>
@@ -7923,22 +7923,22 @@
         <v>135</v>
       </c>
       <c r="D215">
+        <v>21</v>
+      </c>
+      <c r="E215">
         <v>20</v>
-      </c>
-      <c r="E215">
-        <v>19</v>
       </c>
       <c r="F215">
         <v>1</v>
       </c>
       <c r="G215" s="1">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="H215" s="1">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I215" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J215">
         <v>0</v>
@@ -7958,10 +7958,10 @@
         <v>105</v>
       </c>
       <c r="D216">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E216">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F216">
         <v>0</v>
@@ -7990,22 +7990,22 @@
         <v>106</v>
       </c>
       <c r="D217">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E217">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F217">
         <v>12</v>
       </c>
       <c r="G217" s="1">
-        <v>93.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H217" s="1">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I217" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J217">
         <v>0</v>
@@ -8404,7 +8404,7 @@
         <v>131</v>
       </c>
       <c r="D229">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E229">
         <v>24</v>
@@ -8413,19 +8413,19 @@
         <v>4</v>
       </c>
       <c r="G229" s="1">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H229" s="1">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="I229" s="2">
         <v>7.4</v>
       </c>
       <c r="J229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -8471,7 +8471,7 @@
         <v>106</v>
       </c>
       <c r="D231">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E231">
         <v>92</v>
@@ -8480,19 +8480,19 @@
         <v>8</v>
       </c>
       <c r="G231" s="1">
-        <v>92</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H231" s="1">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I231" s="2">
         <v>8.1</v>
       </c>
       <c r="J231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K231" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -8506,7 +8506,7 @@
         <v>135</v>
       </c>
       <c r="D232">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E232">
         <v>11</v>
@@ -8515,19 +8515,19 @@
         <v>9</v>
       </c>
       <c r="G232" s="1">
-        <v>55</v>
+        <v>52.4</v>
       </c>
       <c r="H232" s="1">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="I232" s="2">
         <v>5.5</v>
       </c>
       <c r="J232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K232" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -8611,7 +8611,7 @@
         <v>121</v>
       </c>
       <c r="D235">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E235">
         <v>22</v>
@@ -8620,19 +8620,19 @@
         <v>1</v>
       </c>
       <c r="G235" s="1">
-        <v>95.7</v>
+        <v>91.7</v>
       </c>
       <c r="H235" s="1">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I235" s="2">
         <v>7.6</v>
       </c>
       <c r="J235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -8643,7 +8643,7 @@
         <v>106</v>
       </c>
       <c r="D236">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E236">
         <v>66</v>
@@ -8652,19 +8652,19 @@
         <v>23</v>
       </c>
       <c r="G236" s="1">
-        <v>74.2</v>
+        <v>72.5</v>
       </c>
       <c r="H236" s="1">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="I236" s="2">
         <v>6.6</v>
       </c>
       <c r="J236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K236" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -9019,7 +9019,7 @@
         <v>132</v>
       </c>
       <c r="D247">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E247">
         <v>40</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="G247" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
@@ -9037,10 +9037,10 @@
         <v>9</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K247" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -9051,7 +9051,7 @@
         <v>106</v>
       </c>
       <c r="D248">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E248">
         <v>40</v>
@@ -9060,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="G248" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
@@ -9069,10 +9069,10 @@
         <v>9</v>
       </c>
       <c r="J248">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K248" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -10427,7 +10427,7 @@
         <v>131</v>
       </c>
       <c r="D288">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E288">
         <v>27</v>
@@ -10436,19 +10436,19 @@
         <v>1</v>
       </c>
       <c r="G288" s="1">
-        <v>96.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H288" s="1">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I288" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J288">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K288" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -10497,7 +10497,7 @@
         <v>135</v>
       </c>
       <c r="D290">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E290">
         <v>21</v>
@@ -10506,7 +10506,7 @@
         <v>0</v>
       </c>
       <c r="G290" s="1">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -10515,10 +10515,10 @@
         <v>8</v>
       </c>
       <c r="J290">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K290" s="1">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -10532,7 +10532,7 @@
         <v>135</v>
       </c>
       <c r="D291">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E291">
         <v>19</v>
@@ -10541,19 +10541,19 @@
         <v>2</v>
       </c>
       <c r="G291" s="1">
-        <v>90.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H291" s="1">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="I291" s="2">
         <v>7.4</v>
       </c>
       <c r="J291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K291" s="1">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -10564,7 +10564,7 @@
         <v>106</v>
       </c>
       <c r="D292">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E292">
         <v>106</v>
@@ -10573,19 +10573,19 @@
         <v>17</v>
       </c>
       <c r="G292" s="1">
-        <v>86.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H292" s="1">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="I292" s="2">
         <v>7.6</v>
       </c>
       <c r="J292">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K292" s="1">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -10963,7 +10963,7 @@
         <v>105</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>25</v>
@@ -10972,7 +10972,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -10981,10 +10981,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -10998,10 +10998,10 @@
         <v>105</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -11030,28 +11030,28 @@
         <v>106</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>97.3</v>
+        <v>94.2</v>
       </c>
       <c r="H7" s="1">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -11220,7 +11220,7 @@
         <v>4.2</v>
       </c>
       <c r="I12" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -11287,7 +11287,7 @@
         <v>3.8</v>
       </c>
       <c r="I14" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -11724,16 +11724,16 @@
         <v>37</v>
       </c>
       <c r="E27">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G27" s="1">
-        <v>78.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="H27" s="1">
-        <v>21.6</v>
+        <v>16.2</v>
       </c>
       <c r="I27" s="2">
         <v>7.4</v>
@@ -11759,16 +11759,16 @@
         <v>33</v>
       </c>
       <c r="E28">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
-        <v>81.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>18.2</v>
+        <v>12.1</v>
       </c>
       <c r="I28" s="2">
         <v>7.3</v>
@@ -11861,7 +11861,7 @@
         <v>121</v>
       </c>
       <c r="D31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E31">
         <v>22</v>
@@ -11870,19 +11870,19 @@
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>95.7</v>
+        <v>91.7</v>
       </c>
       <c r="H31" s="1">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I31" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -11893,28 +11893,28 @@
         <v>106</v>
       </c>
       <c r="D32">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F32">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G32" s="1">
-        <v>89.3</v>
+        <v>91.3</v>
       </c>
       <c r="H32" s="1">
-        <v>10.7</v>
+        <v>8</v>
       </c>
       <c r="I32" s="2">
         <v>8</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -11928,7 +11928,7 @@
         <v>105</v>
       </c>
       <c r="D33">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E33">
         <v>25</v>
@@ -11937,7 +11937,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -11946,10 +11946,10 @@
         <v>9.4</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -11960,7 +11960,7 @@
         <v>106</v>
       </c>
       <c r="D34">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E34">
         <v>25</v>
@@ -11969,7 +11969,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -11978,10 +11978,10 @@
         <v>9.4</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -12491,7 +12491,7 @@
         <v>4.9</v>
       </c>
       <c r="I49" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -12514,19 +12514,19 @@
         <v>34</v>
       </c>
       <c r="E50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="1">
-        <v>91.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H50" s="1">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="I50" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -12546,19 +12546,19 @@
         <v>75</v>
       </c>
       <c r="E51">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" s="1">
-        <v>93.3</v>
+        <v>94.7</v>
       </c>
       <c r="H51" s="1">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="I51" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -13795,19 +13795,19 @@
         <v>121</v>
       </c>
       <c r="D95">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E95">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F95">
         <v>4</v>
       </c>
       <c r="G95" s="1">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H95" s="1">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="I95" s="2">
         <v>7.6</v>
@@ -13827,19 +13827,19 @@
         <v>106</v>
       </c>
       <c r="D96">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E96">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F96">
         <v>21</v>
       </c>
       <c r="G96" s="1">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="H96" s="1">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="I96" s="2">
         <v>7.4</v>
@@ -14104,7 +14104,7 @@
         <v>131</v>
       </c>
       <c r="D104">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E104">
         <v>28</v>
@@ -14113,7 +14113,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -14122,10 +14122,10 @@
         <v>9</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -14209,7 +14209,7 @@
         <v>132</v>
       </c>
       <c r="D107">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E107">
         <v>40</v>
@@ -14218,7 +14218,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -14227,10 +14227,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K107" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -14314,7 +14314,7 @@
         <v>121</v>
       </c>
       <c r="D110">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E110">
         <v>23</v>
@@ -14323,7 +14323,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -14332,10 +14332,10 @@
         <v>9</v>
       </c>
       <c r="J110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -14346,7 +14346,7 @@
         <v>106</v>
       </c>
       <c r="D111">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E111">
         <v>231</v>
@@ -14355,19 +14355,19 @@
         <v>2</v>
       </c>
       <c r="G111" s="1">
-        <v>99.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="H111" s="1">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I111" s="2">
         <v>8.9</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K111" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -14900,7 +14900,7 @@
         <v>131</v>
       </c>
       <c r="D127">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E127">
         <v>25</v>
@@ -14909,19 +14909,19 @@
         <v>3</v>
       </c>
       <c r="G127" s="1">
-        <v>89.3</v>
+        <v>86.2</v>
       </c>
       <c r="H127" s="1">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="I127" s="2">
         <v>8.5</v>
       </c>
       <c r="J127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -14935,22 +14935,22 @@
         <v>131</v>
       </c>
       <c r="D128">
+        <v>29</v>
+      </c>
+      <c r="E128">
         <v>28</v>
-      </c>
-      <c r="E128">
-        <v>27</v>
       </c>
       <c r="F128">
         <v>1</v>
       </c>
       <c r="G128" s="1">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H128" s="1">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I128" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -15107,28 +15107,28 @@
         <v>106</v>
       </c>
       <c r="D133">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E133">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F133">
         <v>30</v>
       </c>
       <c r="G133" s="1">
-        <v>88.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H133" s="1">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="I133" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" s="1">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -15279,7 +15279,7 @@
         <v>131</v>
       </c>
       <c r="D138">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E138">
         <v>28</v>
@@ -15288,7 +15288,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="1">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H138" s="1">
         <v>0</v>
@@ -15297,10 +15297,10 @@
         <v>6.8</v>
       </c>
       <c r="J138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K138" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -15314,7 +15314,7 @@
         <v>135</v>
       </c>
       <c r="D139">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E139">
         <v>20</v>
@@ -15323,19 +15323,19 @@
         <v>1</v>
       </c>
       <c r="G139" s="1">
-        <v>95.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H139" s="1">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I139" s="2">
         <v>6.5</v>
       </c>
       <c r="J139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K139" s="1">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -15381,7 +15381,7 @@
         <v>106</v>
       </c>
       <c r="D141">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E141">
         <v>123</v>
@@ -15390,7 +15390,7 @@
         <v>2</v>
       </c>
       <c r="G141" s="1">
-        <v>98.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H141" s="1">
         <v>1.6</v>
@@ -15399,10 +15399,10 @@
         <v>7.6</v>
       </c>
       <c r="J141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K141" s="1">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -15728,7 +15728,7 @@
         <v>121</v>
       </c>
       <c r="D151">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E151">
         <v>23</v>
@@ -15737,7 +15737,7 @@
         <v>0</v>
       </c>
       <c r="G151" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
@@ -15746,10 +15746,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -15760,7 +15760,7 @@
         <v>106</v>
       </c>
       <c r="D152">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E152">
         <v>74</v>
@@ -15769,19 +15769,19 @@
         <v>10</v>
       </c>
       <c r="G152" s="1">
-        <v>88.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H152" s="1">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="I152" s="2">
         <v>8</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -15967,7 +15967,7 @@
         <v>131</v>
       </c>
       <c r="D158">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E158">
         <v>23</v>
@@ -15976,19 +15976,19 @@
         <v>5</v>
       </c>
       <c r="G158" s="1">
-        <v>82.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="H158" s="1">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="I158" s="2">
         <v>7.4</v>
       </c>
       <c r="J158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -16072,7 +16072,7 @@
         <v>132</v>
       </c>
       <c r="D161">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E161">
         <v>32</v>
@@ -16081,19 +16081,19 @@
         <v>8</v>
       </c>
       <c r="G161" s="1">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="H161" s="1">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="I161" s="2">
         <v>7.4</v>
       </c>
       <c r="J161">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K161" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -16157,7 +16157,7 @@
         <v>0</v>
       </c>
       <c r="I163" s="2">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>106</v>
       </c>
       <c r="D164">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E164">
         <v>187</v>
@@ -16183,19 +16183,19 @@
         <v>23</v>
       </c>
       <c r="G164" s="1">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H164" s="1">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="I164" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J164">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K164" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -16279,10 +16279,10 @@
         <v>132</v>
       </c>
       <c r="D167">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E167">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -16294,7 +16294,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -16314,10 +16314,10 @@
         <v>132</v>
       </c>
       <c r="D168">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E168">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F168">
         <v>0</v>
@@ -16329,7 +16329,7 @@
         <v>0</v>
       </c>
       <c r="I168" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>106</v>
       </c>
       <c r="D169">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E169">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -16361,7 +16361,7 @@
         <v>0.7</v>
       </c>
       <c r="I169" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -16448,7 +16448,7 @@
         <v>135</v>
       </c>
       <c r="D172">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E172">
         <v>15</v>
@@ -16457,19 +16457,19 @@
         <v>5</v>
       </c>
       <c r="G172" s="1">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H172" s="1">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="I172" s="2">
         <v>7.5</v>
       </c>
       <c r="J172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -16483,7 +16483,7 @@
         <v>135</v>
       </c>
       <c r="D173">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E173">
         <v>12</v>
@@ -16492,19 +16492,19 @@
         <v>8</v>
       </c>
       <c r="G173" s="1">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="H173" s="1">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="I173" s="2">
         <v>7.6</v>
       </c>
       <c r="J173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K173" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -16588,7 +16588,7 @@
         <v>121</v>
       </c>
       <c r="D176">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E176">
         <v>23</v>
@@ -16597,7 +16597,7 @@
         <v>0</v>
       </c>
       <c r="G176" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K176" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -16623,7 +16623,7 @@
         <v>105</v>
       </c>
       <c r="D177">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E177">
         <v>25</v>
@@ -16632,7 +16632,7 @@
         <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
@@ -16641,10 +16641,10 @@
         <v>8.1</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K177" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -16658,7 +16658,7 @@
         <v>105</v>
       </c>
       <c r="D178">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E178">
         <v>22</v>
@@ -16667,19 +16667,19 @@
         <v>3</v>
       </c>
       <c r="G178" s="1">
-        <v>88</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H178" s="1">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="I178" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J178">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K178" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -16690,7 +16690,7 @@
         <v>106</v>
       </c>
       <c r="D179">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E179">
         <v>123</v>
@@ -16699,19 +16699,19 @@
         <v>26</v>
       </c>
       <c r="G179" s="1">
-        <v>82.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H179" s="1">
-        <v>17.4</v>
+        <v>16.2</v>
       </c>
       <c r="I179" s="2">
         <v>8</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K179" s="1">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -17189,7 +17189,7 @@
         <v>19.5</v>
       </c>
       <c r="I193" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J193">
         <v>0</v>
@@ -17431,7 +17431,7 @@
         <v>10.1</v>
       </c>
       <c r="I200" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -17868,10 +17868,10 @@
         <v>132</v>
       </c>
       <c r="D213">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E213">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -17883,7 +17883,7 @@
         <v>0</v>
       </c>
       <c r="I213" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J213">
         <v>0</v>
@@ -17938,22 +17938,22 @@
         <v>135</v>
       </c>
       <c r="D215">
+        <v>21</v>
+      </c>
+      <c r="E215">
         <v>20</v>
-      </c>
-      <c r="E215">
-        <v>19</v>
       </c>
       <c r="F215">
         <v>1</v>
       </c>
       <c r="G215" s="1">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="H215" s="1">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I215" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J215">
         <v>0</v>
@@ -17973,10 +17973,10 @@
         <v>105</v>
       </c>
       <c r="D216">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E216">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F216">
         <v>0</v>
@@ -17988,7 +17988,7 @@
         <v>0</v>
       </c>
       <c r="I216" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J216">
         <v>0</v>
@@ -18005,22 +18005,22 @@
         <v>106</v>
       </c>
       <c r="D217">
+        <v>204</v>
+      </c>
+      <c r="E217">
         <v>195</v>
-      </c>
-      <c r="E217">
-        <v>186</v>
       </c>
       <c r="F217">
         <v>9</v>
       </c>
       <c r="G217" s="1">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H217" s="1">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I217" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J217">
         <v>0</v>
@@ -18419,7 +18419,7 @@
         <v>131</v>
       </c>
       <c r="D229">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E229">
         <v>24</v>
@@ -18428,19 +18428,19 @@
         <v>4</v>
       </c>
       <c r="G229" s="1">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H229" s="1">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="I229" s="2">
         <v>7.6</v>
       </c>
       <c r="J229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -18486,7 +18486,7 @@
         <v>106</v>
       </c>
       <c r="D231">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E231">
         <v>93</v>
@@ -18495,19 +18495,19 @@
         <v>7</v>
       </c>
       <c r="G231" s="1">
-        <v>93</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H231" s="1">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I231" s="2">
         <v>8</v>
       </c>
       <c r="J231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K231" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -18521,7 +18521,7 @@
         <v>135</v>
       </c>
       <c r="D232">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E232">
         <v>9</v>
@@ -18530,19 +18530,19 @@
         <v>11</v>
       </c>
       <c r="G232" s="1">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="H232" s="1">
-        <v>55</v>
+        <v>52.4</v>
       </c>
       <c r="I232" s="2">
         <v>5.8</v>
       </c>
       <c r="J232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K232" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -18626,7 +18626,7 @@
         <v>121</v>
       </c>
       <c r="D235">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E235">
         <v>23</v>
@@ -18635,7 +18635,7 @@
         <v>0</v>
       </c>
       <c r="G235" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
@@ -18644,10 +18644,10 @@
         <v>8.4</v>
       </c>
       <c r="J235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -18658,7 +18658,7 @@
         <v>106</v>
       </c>
       <c r="D236">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E236">
         <v>68</v>
@@ -18667,19 +18667,19 @@
         <v>21</v>
       </c>
       <c r="G236" s="1">
-        <v>76.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="H236" s="1">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="I236" s="2">
         <v>7</v>
       </c>
       <c r="J236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K236" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -19034,7 +19034,7 @@
         <v>132</v>
       </c>
       <c r="D247">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E247">
         <v>40</v>
@@ -19043,7 +19043,7 @@
         <v>0</v>
       </c>
       <c r="G247" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
@@ -19052,10 +19052,10 @@
         <v>9.4</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K247" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -19066,7 +19066,7 @@
         <v>106</v>
       </c>
       <c r="D248">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E248">
         <v>40</v>
@@ -19075,7 +19075,7 @@
         <v>0</v>
       </c>
       <c r="G248" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
@@ -19084,10 +19084,10 @@
         <v>9.4</v>
       </c>
       <c r="J248">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K248" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -20442,7 +20442,7 @@
         <v>131</v>
       </c>
       <c r="D288">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E288">
         <v>27</v>
@@ -20451,19 +20451,19 @@
         <v>1</v>
       </c>
       <c r="G288" s="1">
-        <v>96.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H288" s="1">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I288" s="2">
         <v>7.2</v>
       </c>
       <c r="J288">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K288" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -20512,7 +20512,7 @@
         <v>135</v>
       </c>
       <c r="D290">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E290">
         <v>21</v>
@@ -20521,7 +20521,7 @@
         <v>0</v>
       </c>
       <c r="G290" s="1">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -20530,10 +20530,10 @@
         <v>7.3</v>
       </c>
       <c r="J290">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K290" s="1">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -20547,7 +20547,7 @@
         <v>135</v>
       </c>
       <c r="D291">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E291">
         <v>19</v>
@@ -20556,19 +20556,19 @@
         <v>2</v>
       </c>
       <c r="G291" s="1">
-        <v>90.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H291" s="1">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="I291" s="2">
         <v>7.7</v>
       </c>
       <c r="J291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K291" s="1">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -20579,7 +20579,7 @@
         <v>106</v>
       </c>
       <c r="D292">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E292">
         <v>111</v>
@@ -20588,19 +20588,19 @@
         <v>12</v>
       </c>
       <c r="G292" s="1">
-        <v>90.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H292" s="1">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I292" s="2">
         <v>7.3</v>
       </c>
       <c r="J292">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K292" s="1">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -20891,10 +20891,10 @@
         <v>9.4</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -20911,25 +20911,25 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -20958,13 +20958,13 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -20978,7 +20978,7 @@
         <v>105</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>25</v>
@@ -20987,7 +20987,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -20996,10 +20996,10 @@
         <v>8.4</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -21013,10 +21013,10 @@
         <v>105</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -21028,13 +21028,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -21045,28 +21045,28 @@
         <v>106</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>97.3</v>
+        <v>96.7</v>
       </c>
       <c r="H7" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -21083,25 +21083,25 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="H8" s="1">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8" s="2">
         <v>8.1</v>
       </c>
       <c r="J8">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -21130,13 +21130,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -21165,13 +21165,13 @@
         <v>3.6</v>
       </c>
       <c r="I10" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -21188,25 +21188,25 @@
         <v>35</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -21223,25 +21223,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J12">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -21258,25 +21258,25 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I13" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -21290,25 +21290,25 @@
         <v>184</v>
       </c>
       <c r="E14">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>96.2</v>
+        <v>97.8</v>
       </c>
       <c r="H14" s="1">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="I14" s="2">
         <v>8.6</v>
       </c>
       <c r="J14">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -21739,25 +21739,25 @@
         <v>37</v>
       </c>
       <c r="E27">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1">
-        <v>78.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>21.6</v>
+        <v>5.4</v>
       </c>
       <c r="I27" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J27">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -21774,25 +21774,25 @@
         <v>33</v>
       </c>
       <c r="E28">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
-        <v>81.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>18.2</v>
+        <v>12.1</v>
       </c>
       <c r="I28" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J28">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -21809,25 +21809,25 @@
         <v>35</v>
       </c>
       <c r="E29">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H29" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -21856,13 +21856,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J30">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -21876,28 +21876,28 @@
         <v>121</v>
       </c>
       <c r="D31">
+        <v>24</v>
+      </c>
+      <c r="E31">
         <v>23</v>
       </c>
-      <c r="E31">
-        <v>22</v>
-      </c>
       <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>95.8</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>9</v>
+      </c>
+      <c r="J31">
         <v>1</v>
       </c>
-      <c r="G31" s="1">
-        <v>95.7</v>
-      </c>
-      <c r="H31" s="1">
-        <v>4.3</v>
-      </c>
-      <c r="I31" s="2">
-        <v>8.9</v>
-      </c>
-      <c r="J31">
-        <v>23</v>
-      </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -21908,28 +21908,28 @@
         <v>106</v>
       </c>
       <c r="D32">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F32">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G32" s="1">
-        <v>89.3</v>
+        <v>95.3</v>
       </c>
       <c r="H32" s="1">
-        <v>10.7</v>
+        <v>4</v>
       </c>
       <c r="I32" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J32">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -21943,7 +21943,7 @@
         <v>105</v>
       </c>
       <c r="D33">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E33">
         <v>25</v>
@@ -21952,7 +21952,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -21961,10 +21961,10 @@
         <v>9.4</v>
       </c>
       <c r="J33">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -21975,7 +21975,7 @@
         <v>106</v>
       </c>
       <c r="D34">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E34">
         <v>25</v>
@@ -21984,7 +21984,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>9.4</v>
       </c>
       <c r="J34">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -22013,25 +22013,25 @@
         <v>40</v>
       </c>
       <c r="E35">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F35">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G35" s="1">
-        <v>60</v>
+        <v>87.5</v>
       </c>
       <c r="H35" s="1">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="I35" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -22083,25 +22083,25 @@
         <v>33</v>
       </c>
       <c r="E37">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1">
-        <v>75.8</v>
+        <v>84.8</v>
       </c>
       <c r="H37" s="1">
-        <v>24.2</v>
+        <v>15.2</v>
       </c>
       <c r="I37" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J37">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -22153,25 +22153,25 @@
         <v>19</v>
       </c>
       <c r="E39">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="H39" s="1">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J39">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -22185,25 +22185,25 @@
         <v>149</v>
       </c>
       <c r="E40">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="F40">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1">
-        <v>68.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H40" s="1">
-        <v>31.5</v>
+        <v>20.1</v>
       </c>
       <c r="I40" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J40">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -22220,25 +22220,25 @@
         <v>24</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H41" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J41">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -22267,13 +22267,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J42">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -22290,25 +22290,25 @@
         <v>28</v>
       </c>
       <c r="E43">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H43" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I43" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J43">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -22325,25 +22325,25 @@
         <v>37</v>
       </c>
       <c r="E44">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H44" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I44" s="2">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J44">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -22357,25 +22357,25 @@
         <v>125</v>
       </c>
       <c r="E45">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G45" s="1">
-        <v>96</v>
+        <v>99.2</v>
       </c>
       <c r="H45" s="1">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="I45" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J45">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -22404,13 +22404,13 @@
         <v>3.6</v>
       </c>
       <c r="I46" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J46">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -22427,25 +22427,25 @@
         <v>19</v>
       </c>
       <c r="E47">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="H47" s="1">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="I47" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J47">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -22459,25 +22459,25 @@
         <v>47</v>
       </c>
       <c r="E48">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="1">
-        <v>93.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="H48" s="1">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="I48" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J48">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -22506,7 +22506,7 @@
         <v>4.9</v>
       </c>
       <c r="I49" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J49">
         <v>41</v>
@@ -22529,19 +22529,19 @@
         <v>34</v>
       </c>
       <c r="E50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="1">
-        <v>91.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H50" s="1">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="I50" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J50">
         <v>34</v>
@@ -22561,19 +22561,19 @@
         <v>75</v>
       </c>
       <c r="E51">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" s="1">
-        <v>93.3</v>
+        <v>94.7</v>
       </c>
       <c r="H51" s="1">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="I51" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J51">
         <v>75</v>
@@ -22678,7 +22678,7 @@
         <v>30.3</v>
       </c>
       <c r="I54" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J54">
         <v>33</v>
@@ -22713,7 +22713,7 @@
         <v>47.8</v>
       </c>
       <c r="I55" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J55">
         <v>23</v>
@@ -23466,25 +23466,25 @@
         <v>34</v>
       </c>
       <c r="E85">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F85">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G85" s="1">
-        <v>50</v>
+        <v>76.5</v>
       </c>
       <c r="H85" s="1">
-        <v>50</v>
+        <v>23.5</v>
       </c>
       <c r="I85" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J85">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -23501,25 +23501,25 @@
         <v>33</v>
       </c>
       <c r="E86">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F86">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G86" s="1">
-        <v>75.8</v>
+        <v>78.8</v>
       </c>
       <c r="H86" s="1">
-        <v>24.2</v>
+        <v>21.2</v>
       </c>
       <c r="I86" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J86">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -23536,25 +23536,25 @@
         <v>23</v>
       </c>
       <c r="E87">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F87">
+        <v>3</v>
+      </c>
+      <c r="G87" s="1">
+        <v>87</v>
+      </c>
+      <c r="H87" s="1">
         <v>13</v>
       </c>
-      <c r="G87" s="1">
-        <v>43.5</v>
-      </c>
-      <c r="H87" s="1">
-        <v>56.5</v>
-      </c>
       <c r="I87" s="2">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="J87">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -23571,25 +23571,25 @@
         <v>19</v>
       </c>
       <c r="E88">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G88" s="1">
-        <v>89.5</v>
+        <v>100</v>
       </c>
       <c r="H88" s="1">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="I88" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J88">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -23606,25 +23606,25 @@
         <v>25</v>
       </c>
       <c r="E89">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G89" s="1">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H89" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I89" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J89">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -23638,25 +23638,25 @@
         <v>134</v>
       </c>
       <c r="E90">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="F90">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G90" s="1">
-        <v>67.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H90" s="1">
-        <v>32.1</v>
+        <v>14.9</v>
       </c>
       <c r="I90" s="2">
         <v>6.7</v>
       </c>
       <c r="J90">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -23810,19 +23810,19 @@
         <v>121</v>
       </c>
       <c r="D95">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E95">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F95">
         <v>4</v>
       </c>
       <c r="G95" s="1">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H95" s="1">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="I95" s="2">
         <v>7.5</v>
@@ -23831,7 +23831,7 @@
         <v>23</v>
       </c>
       <c r="K95" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -23842,19 +23842,19 @@
         <v>106</v>
       </c>
       <c r="D96">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E96">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F96">
         <v>21</v>
       </c>
       <c r="G96" s="1">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="H96" s="1">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="I96" s="2">
         <v>7.3</v>
@@ -23863,7 +23863,7 @@
         <v>108</v>
       </c>
       <c r="K96" s="1">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -24119,7 +24119,7 @@
         <v>131</v>
       </c>
       <c r="D104">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E104">
         <v>28</v>
@@ -24128,19 +24128,19 @@
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J104">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K104" s="1">
-        <v>100</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -24169,13 +24169,13 @@
         <v>0</v>
       </c>
       <c r="I105" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J105">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -24224,28 +24224,28 @@
         <v>132</v>
       </c>
       <c r="D107">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E107">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G107" s="1">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I107" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J107">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="K107" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -24274,13 +24274,13 @@
         <v>0</v>
       </c>
       <c r="I108" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J108">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -24329,7 +24329,7 @@
         <v>121</v>
       </c>
       <c r="D110">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E110">
         <v>23</v>
@@ -24338,19 +24338,19 @@
         <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
       </c>
       <c r="I110" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J110">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K110" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -24361,28 +24361,28 @@
         <v>106</v>
       </c>
       <c r="D111">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E111">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F111">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G111" s="1">
-        <v>99.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="H111" s="1">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="I111" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J111">
-        <v>233</v>
+        <v>76</v>
       </c>
       <c r="K111" s="1">
-        <v>100</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -24551,13 +24551,13 @@
         <v>4.8</v>
       </c>
       <c r="I116" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J116">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K116" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -24586,10 +24586,10 @@
         <v>7.9</v>
       </c>
       <c r="J117">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="K117" s="1">
-        <v>100</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -24915,7 +24915,7 @@
         <v>131</v>
       </c>
       <c r="D127">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E127">
         <v>25</v>
@@ -24924,16 +24924,16 @@
         <v>3</v>
       </c>
       <c r="G127" s="1">
-        <v>89.3</v>
+        <v>86.2</v>
       </c>
       <c r="H127" s="1">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="I127" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J127">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K127" s="1">
         <v>100</v>
@@ -24950,28 +24950,28 @@
         <v>131</v>
       </c>
       <c r="D128">
+        <v>29</v>
+      </c>
+      <c r="E128">
         <v>28</v>
-      </c>
-      <c r="E128">
-        <v>27</v>
       </c>
       <c r="F128">
         <v>1</v>
       </c>
       <c r="G128" s="1">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H128" s="1">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I128" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J128">
         <v>28</v>
       </c>
       <c r="K128" s="1">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -25122,28 +25122,28 @@
         <v>106</v>
       </c>
       <c r="D133">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E133">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F133">
         <v>30</v>
       </c>
       <c r="G133" s="1">
-        <v>88.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H133" s="1">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="I133" s="2">
         <v>8.1</v>
       </c>
       <c r="J133">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K133" s="1">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -25172,7 +25172,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I134" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J134">
         <v>41</v>
@@ -25204,7 +25204,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I135" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J135">
         <v>41</v>
@@ -25242,10 +25242,10 @@
         <v>8</v>
       </c>
       <c r="J136">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K136" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -25277,10 +25277,10 @@
         <v>8</v>
       </c>
       <c r="J137">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K137" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -25294,7 +25294,7 @@
         <v>131</v>
       </c>
       <c r="D138">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E138">
         <v>28</v>
@@ -25303,7 +25303,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="1">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H138" s="1">
         <v>0</v>
@@ -25312,7 +25312,7 @@
         <v>7.6</v>
       </c>
       <c r="J138">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K138" s="1">
         <v>100</v>
@@ -25329,7 +25329,7 @@
         <v>135</v>
       </c>
       <c r="D139">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E139">
         <v>20</v>
@@ -25338,16 +25338,16 @@
         <v>1</v>
       </c>
       <c r="G139" s="1">
-        <v>95.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H139" s="1">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I139" s="2">
         <v>7.5</v>
       </c>
       <c r="J139">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K139" s="1">
         <v>100</v>
@@ -25396,7 +25396,7 @@
         <v>106</v>
       </c>
       <c r="D141">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E141">
         <v>123</v>
@@ -25405,7 +25405,7 @@
         <v>2</v>
       </c>
       <c r="G141" s="1">
-        <v>98.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H141" s="1">
         <v>1.6</v>
@@ -25414,10 +25414,10 @@
         <v>7.9</v>
       </c>
       <c r="J141">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="K141" s="1">
-        <v>100</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -25743,7 +25743,7 @@
         <v>121</v>
       </c>
       <c r="D151">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E151">
         <v>23</v>
@@ -25752,7 +25752,7 @@
         <v>0</v>
       </c>
       <c r="G151" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
@@ -25761,7 +25761,7 @@
         <v>8.9</v>
       </c>
       <c r="J151">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K151" s="1">
         <v>100</v>
@@ -25775,7 +25775,7 @@
         <v>106</v>
       </c>
       <c r="D152">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E152">
         <v>74</v>
@@ -25784,16 +25784,16 @@
         <v>10</v>
       </c>
       <c r="G152" s="1">
-        <v>88.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H152" s="1">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="I152" s="2">
         <v>8.1</v>
       </c>
       <c r="J152">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K152" s="1">
         <v>100</v>
@@ -25828,10 +25828,10 @@
         <v>9.1</v>
       </c>
       <c r="J153">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -25860,13 +25860,13 @@
         <v>3.6</v>
       </c>
       <c r="I154" s="2">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J154">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -25895,13 +25895,13 @@
         <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J155">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K155" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -25933,10 +25933,10 @@
         <v>9.1</v>
       </c>
       <c r="J156">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -25962,13 +25962,13 @@
         <v>0.9</v>
       </c>
       <c r="I157" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J157">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K157" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -25982,7 +25982,7 @@
         <v>131</v>
       </c>
       <c r="D158">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E158">
         <v>23</v>
@@ -25991,16 +25991,16 @@
         <v>5</v>
       </c>
       <c r="G158" s="1">
-        <v>82.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="H158" s="1">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="I158" s="2">
         <v>7.4</v>
       </c>
       <c r="J158">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K158" s="1">
         <v>100</v>
@@ -26087,7 +26087,7 @@
         <v>132</v>
       </c>
       <c r="D161">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E161">
         <v>32</v>
@@ -26096,16 +26096,16 @@
         <v>8</v>
       </c>
       <c r="G161" s="1">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="H161" s="1">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="I161" s="2">
         <v>7.3</v>
       </c>
       <c r="J161">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K161" s="1">
         <v>100</v>
@@ -26172,7 +26172,7 @@
         <v>0</v>
       </c>
       <c r="I163" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J163">
         <v>36</v>
@@ -26189,7 +26189,7 @@
         <v>106</v>
       </c>
       <c r="D164">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E164">
         <v>187</v>
@@ -26198,16 +26198,16 @@
         <v>23</v>
       </c>
       <c r="G164" s="1">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H164" s="1">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="I164" s="2">
         <v>7.6</v>
       </c>
       <c r="J164">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K164" s="1">
         <v>100</v>
@@ -26239,13 +26239,13 @@
         <v>0</v>
       </c>
       <c r="I165" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J165">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K165" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -26274,13 +26274,13 @@
         <v>4.8</v>
       </c>
       <c r="I166" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J166">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -26294,10 +26294,10 @@
         <v>132</v>
       </c>
       <c r="D167">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E167">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -26309,13 +26309,13 @@
         <v>0</v>
       </c>
       <c r="I167" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J167">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K167" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -26329,10 +26329,10 @@
         <v>132</v>
       </c>
       <c r="D168">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E168">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F168">
         <v>0</v>
@@ -26344,13 +26344,13 @@
         <v>0</v>
       </c>
       <c r="I168" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J168">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K168" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -26361,10 +26361,10 @@
         <v>106</v>
       </c>
       <c r="D169">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E169">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -26379,10 +26379,10 @@
         <v>8</v>
       </c>
       <c r="J169">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="K169" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -26463,28 +26463,28 @@
         <v>135</v>
       </c>
       <c r="D172">
+        <v>21</v>
+      </c>
+      <c r="E172">
         <v>20</v>
       </c>
-      <c r="E172">
-        <v>15</v>
-      </c>
       <c r="F172">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>75</v>
+        <v>95.2</v>
       </c>
       <c r="H172" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I172" s="2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J172">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K172" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -26498,28 +26498,28 @@
         <v>135</v>
       </c>
       <c r="D173">
+        <v>21</v>
+      </c>
+      <c r="E173">
         <v>20</v>
       </c>
-      <c r="E173">
-        <v>12</v>
-      </c>
       <c r="F173">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G173" s="1">
-        <v>60</v>
+        <v>95.2</v>
       </c>
       <c r="H173" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I173" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J173">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K173" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -26536,25 +26536,25 @@
         <v>18</v>
       </c>
       <c r="E174">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F174">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G174" s="1">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="H174" s="1">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="I174" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J174">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K174" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -26571,25 +26571,25 @@
         <v>18</v>
       </c>
       <c r="E175">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F175">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G175" s="1">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="H175" s="1">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="I175" s="2">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="J175">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K175" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -26603,7 +26603,7 @@
         <v>121</v>
       </c>
       <c r="D176">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E176">
         <v>23</v>
@@ -26612,19 +26612,19 @@
         <v>0</v>
       </c>
       <c r="G176" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
       </c>
       <c r="I176" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J176">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K176" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -26638,28 +26638,28 @@
         <v>105</v>
       </c>
       <c r="D177">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E177">
         <v>25</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G177" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H177" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I177" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J177">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K177" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -26673,28 +26673,28 @@
         <v>105</v>
       </c>
       <c r="D178">
+        <v>29</v>
+      </c>
+      <c r="E178">
         <v>25</v>
       </c>
-      <c r="E178">
-        <v>22</v>
-      </c>
       <c r="F178">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G178" s="1">
-        <v>88</v>
+        <v>86.2</v>
       </c>
       <c r="H178" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I178" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J178">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K178" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -26705,28 +26705,28 @@
         <v>106</v>
       </c>
       <c r="D179">
+        <v>160</v>
+      </c>
+      <c r="E179">
         <v>149</v>
       </c>
-      <c r="E179">
-        <v>123</v>
-      </c>
       <c r="F179">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G179" s="1">
-        <v>82.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H179" s="1">
-        <v>17.4</v>
+        <v>2.5</v>
       </c>
       <c r="I179" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J179">
-        <v>149</v>
+        <v>11</v>
       </c>
       <c r="K179" s="1">
-        <v>100</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -26985,25 +26985,25 @@
         <v>25</v>
       </c>
       <c r="E187">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F187">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G187" s="1">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H187" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I187" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J187">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -27020,25 +27020,25 @@
         <v>19</v>
       </c>
       <c r="E188">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G188" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="H188" s="1">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="I188" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J188">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -27055,25 +27055,25 @@
         <v>21</v>
       </c>
       <c r="E189">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189" s="1">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="H189" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I189" s="2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J189">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -27102,13 +27102,13 @@
         <v>0</v>
       </c>
       <c r="I190" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J190">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -27122,25 +27122,25 @@
         <v>75</v>
       </c>
       <c r="E191">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F191">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G191" s="1">
-        <v>90.7</v>
+        <v>94.7</v>
       </c>
       <c r="H191" s="1">
-        <v>9.300000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="I191" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J191">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -27157,25 +27157,25 @@
         <v>40</v>
       </c>
       <c r="E192">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F192">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G192" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H192" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I192" s="2">
         <v>8.5</v>
       </c>
       <c r="J192">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K192" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -27192,25 +27192,25 @@
         <v>41</v>
       </c>
       <c r="E193">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F193">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G193" s="1">
-        <v>78</v>
+        <v>92.7</v>
       </c>
       <c r="H193" s="1">
-        <v>22</v>
+        <v>7.3</v>
       </c>
       <c r="I193" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J193">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K193" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -27227,25 +27227,25 @@
         <v>48</v>
       </c>
       <c r="E194">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F194">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G194" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H194" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I194" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J194">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -27274,13 +27274,13 @@
         <v>2.8</v>
       </c>
       <c r="I195" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J195">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -27297,25 +27297,25 @@
         <v>37</v>
       </c>
       <c r="E196">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F196">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G196" s="1">
-        <v>81.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H196" s="1">
-        <v>18.9</v>
+        <v>5.4</v>
       </c>
       <c r="I196" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J196">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K196" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -27332,25 +27332,25 @@
         <v>33</v>
       </c>
       <c r="E197">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F197">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G197" s="1">
-        <v>87.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="H197" s="1">
-        <v>12.1</v>
+        <v>3</v>
       </c>
       <c r="I197" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J197">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -27367,25 +27367,25 @@
         <v>36</v>
       </c>
       <c r="E198">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G198" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H198" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I198" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J198">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -27417,10 +27417,10 @@
         <v>8.9</v>
       </c>
       <c r="J199">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -27434,25 +27434,25 @@
         <v>306</v>
       </c>
       <c r="E200">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="F200">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G200" s="1">
-        <v>89.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H200" s="1">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="I200" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J200">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="K200" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -27469,25 +27469,25 @@
         <v>40</v>
       </c>
       <c r="E201">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F201">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G201" s="1">
-        <v>77.5</v>
+        <v>97.5</v>
       </c>
       <c r="H201" s="1">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="I201" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J201">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K201" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -27516,13 +27516,13 @@
         <v>0</v>
       </c>
       <c r="I202" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J202">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -27551,13 +27551,13 @@
         <v>2.8</v>
       </c>
       <c r="I203" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J203">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -27574,25 +27574,25 @@
         <v>40</v>
       </c>
       <c r="E204">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F204">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G204" s="1">
-        <v>77.5</v>
+        <v>97.5</v>
       </c>
       <c r="H204" s="1">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="I204" s="2">
         <v>6.8</v>
       </c>
       <c r="J204">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -27609,25 +27609,25 @@
         <v>34</v>
       </c>
       <c r="E205">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F205">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G205" s="1">
-        <v>82.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H205" s="1">
-        <v>17.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I205" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J205">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -27644,25 +27644,25 @@
         <v>33</v>
       </c>
       <c r="E206">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F206">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G206" s="1">
-        <v>78.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H206" s="1">
-        <v>21.2</v>
+        <v>9.1</v>
       </c>
       <c r="I206" s="2">
         <v>6.9</v>
       </c>
       <c r="J206">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K206" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -27679,25 +27679,25 @@
         <v>23</v>
       </c>
       <c r="E207">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F207">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G207" s="1">
-        <v>82.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H207" s="1">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="I207" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J207">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K207" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -27726,13 +27726,13 @@
         <v>0</v>
       </c>
       <c r="I208" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J208">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K208" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -27761,13 +27761,13 @@
         <v>0</v>
       </c>
       <c r="I209" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J209">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K209" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -27781,25 +27781,25 @@
         <v>309</v>
       </c>
       <c r="E210">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="F210">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G210" s="1">
-        <v>88.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H210" s="1">
-        <v>11.7</v>
+        <v>2.9</v>
       </c>
       <c r="I210" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J210">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="K210" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -27883,10 +27883,10 @@
         <v>132</v>
       </c>
       <c r="D213">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E213">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -27898,13 +27898,13 @@
         <v>0</v>
       </c>
       <c r="I213" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J213">
         <v>40</v>
       </c>
       <c r="K213" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -27933,13 +27933,13 @@
         <v>0</v>
       </c>
       <c r="I214" s="2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J214">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K214" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -27953,19 +27953,19 @@
         <v>135</v>
       </c>
       <c r="D215">
+        <v>21</v>
+      </c>
+      <c r="E215">
         <v>20</v>
-      </c>
-      <c r="E215">
-        <v>19</v>
       </c>
       <c r="F215">
         <v>1</v>
       </c>
       <c r="G215" s="1">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="H215" s="1">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I215" s="2">
         <v>8.300000000000001</v>
@@ -27974,7 +27974,7 @@
         <v>20</v>
       </c>
       <c r="K215" s="1">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -27988,10 +27988,10 @@
         <v>105</v>
       </c>
       <c r="D216">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E216">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F216">
         <v>0</v>
@@ -28003,13 +28003,13 @@
         <v>0</v>
       </c>
       <c r="I216" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J216">
         <v>25</v>
       </c>
       <c r="K216" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -28020,28 +28020,28 @@
         <v>106</v>
       </c>
       <c r="D217">
+        <v>204</v>
+      </c>
+      <c r="E217">
         <v>195</v>
-      </c>
-      <c r="E217">
-        <v>186</v>
       </c>
       <c r="F217">
         <v>9</v>
       </c>
       <c r="G217" s="1">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H217" s="1">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I217" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J217">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="K217" s="1">
-        <v>100</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -28058,25 +28058,25 @@
         <v>24</v>
       </c>
       <c r="E218">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F218">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G218" s="1">
-        <v>79.2</v>
+        <v>83.3</v>
       </c>
       <c r="H218" s="1">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="I218" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J218">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K218" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -28093,25 +28093,25 @@
         <v>36</v>
       </c>
       <c r="E219">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G219" s="1">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H219" s="1">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I219" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J219">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K219" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -28128,25 +28128,25 @@
         <v>35</v>
       </c>
       <c r="E220">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G220" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H220" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I220" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J220">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K220" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -28175,13 +28175,13 @@
         <v>0</v>
       </c>
       <c r="I221" s="2">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J221">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K221" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -28207,13 +28207,13 @@
         <v>5</v>
       </c>
       <c r="I222" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J222">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="K222" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:11">
@@ -28230,25 +28230,25 @@
         <v>25</v>
       </c>
       <c r="E223">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F223">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G223" s="1">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H223" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I223" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J223">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K223" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -28265,25 +28265,25 @@
         <v>19</v>
       </c>
       <c r="E224">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G224" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="H224" s="1">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="I224" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J224">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K224" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:11">
@@ -28300,25 +28300,25 @@
         <v>28</v>
       </c>
       <c r="E225">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F225">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G225" s="1">
-        <v>92.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H225" s="1">
-        <v>7.1</v>
+        <v>21.4</v>
       </c>
       <c r="I225" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J225">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K225" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -28332,25 +28332,25 @@
         <v>72</v>
       </c>
       <c r="E226">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F226">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G226" s="1">
-        <v>91.7</v>
+        <v>90.3</v>
       </c>
       <c r="H226" s="1">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I226" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J226">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="K226" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -28434,7 +28434,7 @@
         <v>131</v>
       </c>
       <c r="D229">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E229">
         <v>24</v>
@@ -28443,16 +28443,16 @@
         <v>4</v>
       </c>
       <c r="G229" s="1">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H229" s="1">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="I229" s="2">
         <v>7.6</v>
       </c>
       <c r="J229">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K229" s="1">
         <v>100</v>
@@ -28501,7 +28501,7 @@
         <v>106</v>
       </c>
       <c r="D231">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E231">
         <v>93</v>
@@ -28510,16 +28510,16 @@
         <v>7</v>
       </c>
       <c r="G231" s="1">
-        <v>93</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H231" s="1">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I231" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J231">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K231" s="1">
         <v>100</v>
@@ -28536,28 +28536,28 @@
         <v>135</v>
       </c>
       <c r="D232">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E232">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F232">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G232" s="1">
-        <v>45</v>
+        <v>76.2</v>
       </c>
       <c r="H232" s="1">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="I232" s="2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J232">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K232" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -28641,7 +28641,7 @@
         <v>121</v>
       </c>
       <c r="D235">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E235">
         <v>23</v>
@@ -28650,7 +28650,7 @@
         <v>0</v>
       </c>
       <c r="G235" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
@@ -28659,7 +28659,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J235">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K235" s="1">
         <v>100</v>
@@ -28673,28 +28673,28 @@
         <v>106</v>
       </c>
       <c r="D236">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E236">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F236">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G236" s="1">
-        <v>76.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H236" s="1">
-        <v>23.6</v>
+        <v>15.4</v>
       </c>
       <c r="I236" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J236">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="K236" s="1">
-        <v>100</v>
+        <v>78</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -29000,10 +29000,10 @@
         <v>9.6</v>
       </c>
       <c r="J245">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K245" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -29032,10 +29032,10 @@
         <v>9.6</v>
       </c>
       <c r="J246">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K246" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -29049,7 +29049,7 @@
         <v>132</v>
       </c>
       <c r="D247">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E247">
         <v>40</v>
@@ -29058,19 +29058,19 @@
         <v>0</v>
       </c>
       <c r="G247" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
       </c>
       <c r="I247" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J247">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K247" s="1">
-        <v>100</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -29081,7 +29081,7 @@
         <v>106</v>
       </c>
       <c r="D248">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E248">
         <v>40</v>
@@ -29090,19 +29090,19 @@
         <v>0</v>
       </c>
       <c r="G248" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
       </c>
       <c r="I248" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J248">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K248" s="1">
-        <v>100</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -29373,13 +29373,13 @@
         <v>5.3</v>
       </c>
       <c r="I256" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J256">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K256" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -29396,25 +29396,25 @@
         <v>18</v>
       </c>
       <c r="E257">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G257" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H257" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I257" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J257">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K257" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -29428,25 +29428,25 @@
         <v>37</v>
       </c>
       <c r="E258">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G258" s="1">
-        <v>94.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="H258" s="1">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="I258" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J258">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K258" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -29475,13 +29475,13 @@
         <v>0</v>
       </c>
       <c r="I259" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J259">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K259" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -29513,10 +29513,10 @@
         <v>7.8</v>
       </c>
       <c r="J260">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K260" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -29542,13 +29542,13 @@
         <v>0</v>
       </c>
       <c r="I261" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J261">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K261" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -29565,25 +29565,25 @@
         <v>28</v>
       </c>
       <c r="E262">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F262">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G262" s="1">
-        <v>78.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H262" s="1">
-        <v>21.4</v>
+        <v>17.9</v>
       </c>
       <c r="I262" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J262">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K262" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -29597,25 +29597,25 @@
         <v>28</v>
       </c>
       <c r="E263">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F263">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G263" s="1">
-        <v>78.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H263" s="1">
-        <v>21.4</v>
+        <v>17.9</v>
       </c>
       <c r="I263" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J263">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K263" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -30183,25 +30183,25 @@
         <v>39</v>
       </c>
       <c r="E280">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F280">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G280" s="1">
-        <v>64.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="H280" s="1">
-        <v>35.9</v>
+        <v>7.7</v>
       </c>
       <c r="I280" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J280">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K280" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -30218,25 +30218,25 @@
         <v>34</v>
       </c>
       <c r="E281">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F281">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G281" s="1">
-        <v>35.3</v>
+        <v>91.2</v>
       </c>
       <c r="H281" s="1">
-        <v>64.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I281" s="2">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J281">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K281" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -30253,25 +30253,25 @@
         <v>23</v>
       </c>
       <c r="E282">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F282">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G282" s="1">
-        <v>43.5</v>
+        <v>100</v>
       </c>
       <c r="H282" s="1">
-        <v>56.5</v>
+        <v>0</v>
       </c>
       <c r="I282" s="2">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="J282">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K282" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -30288,25 +30288,25 @@
         <v>19</v>
       </c>
       <c r="E283">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F283">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G283" s="1">
-        <v>78.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="H283" s="1">
-        <v>21.1</v>
+        <v>5.3</v>
       </c>
       <c r="I283" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J283">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K283" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -30323,25 +30323,25 @@
         <v>19</v>
       </c>
       <c r="E284">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F284">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G284" s="1">
-        <v>63.2</v>
+        <v>94.7</v>
       </c>
       <c r="H284" s="1">
-        <v>36.8</v>
+        <v>5.3</v>
       </c>
       <c r="I284" s="2">
         <v>7.2</v>
       </c>
       <c r="J284">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K284" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -30358,25 +30358,25 @@
         <v>10</v>
       </c>
       <c r="E285">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F285">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G285" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H285" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I285" s="2">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="J285">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K285" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -30390,25 +30390,25 @@
         <v>144</v>
       </c>
       <c r="E286">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="F286">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="G286" s="1">
-        <v>56.9</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H286" s="1">
-        <v>43.1</v>
+        <v>5.6</v>
       </c>
       <c r="I286" s="2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J286">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="K286" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -30457,7 +30457,7 @@
         <v>131</v>
       </c>
       <c r="D288">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E288">
         <v>27</v>
@@ -30466,16 +30466,16 @@
         <v>1</v>
       </c>
       <c r="G288" s="1">
-        <v>96.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H288" s="1">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I288" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J288">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K288" s="1">
         <v>100</v>
@@ -30527,7 +30527,7 @@
         <v>135</v>
       </c>
       <c r="D290">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E290">
         <v>21</v>
@@ -30536,7 +30536,7 @@
         <v>0</v>
       </c>
       <c r="G290" s="1">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -30545,7 +30545,7 @@
         <v>7.8</v>
       </c>
       <c r="J290">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K290" s="1">
         <v>100</v>
@@ -30562,7 +30562,7 @@
         <v>135</v>
       </c>
       <c r="D291">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E291">
         <v>19</v>
@@ -30571,16 +30571,16 @@
         <v>2</v>
       </c>
       <c r="G291" s="1">
-        <v>90.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H291" s="1">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="I291" s="2">
         <v>7.7</v>
       </c>
       <c r="J291">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K291" s="1">
         <v>100</v>
@@ -30594,7 +30594,7 @@
         <v>106</v>
       </c>
       <c r="D292">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E292">
         <v>111</v>
@@ -30603,16 +30603,16 @@
         <v>12</v>
       </c>
       <c r="G292" s="1">
-        <v>90.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H292" s="1">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I292" s="2">
         <v>7.6</v>
       </c>
       <c r="J292">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K292" s="1">
         <v>100</v>
@@ -30644,13 +30644,13 @@
         <v>0</v>
       </c>
       <c r="I293" s="2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J293">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K293" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -30679,13 +30679,13 @@
         <v>0</v>
       </c>
       <c r="I294" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J294">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K294" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -30714,13 +30714,13 @@
         <v>0</v>
       </c>
       <c r="I295" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J295">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K295" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -30752,10 +30752,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J296">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K296" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:11">
@@ -30787,10 +30787,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J297">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K297" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:11">
@@ -30816,13 +30816,13 @@
         <v>0</v>
       </c>
       <c r="I298" s="2">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J298">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="K298" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/DetalleXDocente20241.xlsx
+++ b/DetalleXDocente20241.xlsx
@@ -5716,13 +5716,13 @@
         <v>24</v>
       </c>
       <c r="E151">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F151">
         <v>1</v>
       </c>
       <c r="G151" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H151" s="1">
         <v>4.2</v>
@@ -5731,10 +5731,10 @@
         <v>8.5</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -5748,13 +5748,13 @@
         <v>85</v>
       </c>
       <c r="E152">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F152">
         <v>11</v>
       </c>
       <c r="G152" s="1">
-        <v>85.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H152" s="1">
         <v>12.9</v>
@@ -5763,10 +5763,10 @@
         <v>7.6</v>
       </c>
       <c r="J152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -15731,13 +15731,13 @@
         <v>24</v>
       </c>
       <c r="E151">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F151">
         <v>0</v>
       </c>
       <c r="G151" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
@@ -15746,10 +15746,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -15763,13 +15763,13 @@
         <v>85</v>
       </c>
       <c r="E152">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F152">
         <v>10</v>
       </c>
       <c r="G152" s="1">
-        <v>87.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H152" s="1">
         <v>11.8</v>
@@ -15778,10 +15778,10 @@
         <v>8</v>
       </c>
       <c r="J152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -21325,25 +21325,25 @@
         <v>39</v>
       </c>
       <c r="E15">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>89.7</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="I15" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J15">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -21360,25 +21360,25 @@
         <v>34</v>
       </c>
       <c r="E16">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>91.2</v>
+        <v>88.2</v>
       </c>
       <c r="H16" s="1">
-        <v>8.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="I16" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -21395,25 +21395,25 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>81.8</v>
+        <v>72.7</v>
       </c>
       <c r="H17" s="1">
-        <v>18.2</v>
+        <v>27.3</v>
       </c>
       <c r="I17" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J17">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -21430,25 +21430,25 @@
         <v>23</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="I18" s="2">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J18">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -21465,25 +21465,25 @@
         <v>19</v>
       </c>
       <c r="E19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>100</v>
+        <v>94.7</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I19" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -21515,10 +21515,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -21532,25 +21532,25 @@
         <v>158</v>
       </c>
       <c r="E21">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G21" s="1">
-        <v>94.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>5.7</v>
+        <v>14.6</v>
       </c>
       <c r="I21" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J21">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -21567,25 +21567,25 @@
         <v>36</v>
       </c>
       <c r="E22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -21602,25 +21602,25 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J23">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -21637,25 +21637,25 @@
         <v>37</v>
       </c>
       <c r="E24">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J24">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -21672,25 +21672,25 @@
         <v>37</v>
       </c>
       <c r="E25">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J25">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -21704,25 +21704,25 @@
         <v>146</v>
       </c>
       <c r="E26">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J26">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -22048,25 +22048,25 @@
         <v>34</v>
       </c>
       <c r="E36">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F36">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1">
-        <v>52.9</v>
+        <v>85.3</v>
       </c>
       <c r="H36" s="1">
-        <v>47.1</v>
+        <v>14.7</v>
       </c>
       <c r="I36" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="J36">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -22118,25 +22118,25 @@
         <v>23</v>
       </c>
       <c r="E38">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1">
-        <v>82.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="H38" s="1">
-        <v>17.4</v>
+        <v>4.3</v>
       </c>
       <c r="I38" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J38">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -22185,25 +22185,25 @@
         <v>149</v>
       </c>
       <c r="E40">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="F40">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G40" s="1">
-        <v>79.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="H40" s="1">
-        <v>20.1</v>
+        <v>10.7</v>
       </c>
       <c r="I40" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J40">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>38.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -22608,13 +22608,13 @@
         <v>17.5</v>
       </c>
       <c r="I52" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J52">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -22631,25 +22631,25 @@
         <v>34</v>
       </c>
       <c r="E53">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F53">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G53" s="1">
-        <v>67.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H53" s="1">
-        <v>32.4</v>
+        <v>17.6</v>
       </c>
       <c r="I53" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J53">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -22666,25 +22666,25 @@
         <v>33</v>
       </c>
       <c r="E54">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F54">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G54" s="1">
-        <v>69.7</v>
+        <v>75.8</v>
       </c>
       <c r="H54" s="1">
-        <v>30.3</v>
+        <v>24.2</v>
       </c>
       <c r="I54" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J54">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -22736,25 +22736,25 @@
         <v>19</v>
       </c>
       <c r="E56">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" s="1">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="H56" s="1">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="I56" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J56">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -22803,25 +22803,25 @@
         <v>170</v>
       </c>
       <c r="E58">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F58">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G58" s="1">
-        <v>68.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H58" s="1">
-        <v>31.8</v>
+        <v>27.1</v>
       </c>
       <c r="I58" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J58">
-        <v>170</v>
+        <v>44</v>
       </c>
       <c r="K58" s="1">
-        <v>100</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -23364,25 +23364,25 @@
         <v>25</v>
       </c>
       <c r="E82">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1">
+        <v>96</v>
+      </c>
+      <c r="H82" s="1">
         <v>4</v>
       </c>
-      <c r="G82" s="1">
-        <v>84</v>
-      </c>
-      <c r="H82" s="1">
-        <v>16</v>
-      </c>
       <c r="I82" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J82">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -23399,25 +23399,25 @@
         <v>28</v>
       </c>
       <c r="E83">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" s="1">
-        <v>89.3</v>
+        <v>85.7</v>
       </c>
       <c r="H83" s="1">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="I83" s="2">
         <v>7.6</v>
       </c>
       <c r="J83">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -23431,25 +23431,25 @@
         <v>53</v>
       </c>
       <c r="E84">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F84">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G84" s="1">
-        <v>86.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H84" s="1">
-        <v>13.2</v>
+        <v>9.4</v>
       </c>
       <c r="I84" s="2">
         <v>7.4</v>
       </c>
       <c r="J84">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -23673,25 +23673,25 @@
         <v>21</v>
       </c>
       <c r="E91">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F91">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G91" s="1">
-        <v>61.9</v>
+        <v>85.7</v>
       </c>
       <c r="H91" s="1">
-        <v>38.1</v>
+        <v>14.3</v>
       </c>
       <c r="I91" s="2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="J91">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -23708,25 +23708,25 @@
         <v>25</v>
       </c>
       <c r="E92">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G92" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H92" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I92" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J92">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K92" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -23755,13 +23755,13 @@
         <v>4.8</v>
       </c>
       <c r="I93" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J93">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -23845,25 +23845,25 @@
         <v>109</v>
       </c>
       <c r="E96">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F96">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G96" s="1">
-        <v>80.7</v>
+        <v>87.2</v>
       </c>
       <c r="H96" s="1">
-        <v>19.3</v>
+        <v>12.8</v>
       </c>
       <c r="I96" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J96">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="K96" s="1">
-        <v>99.09999999999999</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -23880,25 +23880,25 @@
         <v>40</v>
       </c>
       <c r="E97">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" s="1">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="H97" s="1">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="I97" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J97">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -23915,25 +23915,25 @@
         <v>41</v>
       </c>
       <c r="E98">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F98">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G98" s="1">
-        <v>87.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H98" s="1">
-        <v>12.2</v>
+        <v>2.4</v>
       </c>
       <c r="I98" s="2">
         <v>6.8</v>
       </c>
       <c r="J98">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -23950,25 +23950,25 @@
         <v>48</v>
       </c>
       <c r="E99">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F99">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G99" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H99" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I99" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J99">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K99" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -24055,25 +24055,25 @@
         <v>33</v>
       </c>
       <c r="E102">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G102" s="1">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="H102" s="1">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="I102" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J102">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K102" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -24087,25 +24087,25 @@
         <v>235</v>
       </c>
       <c r="E103">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F103">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G103" s="1">
-        <v>91.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H103" s="1">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="I103" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J103">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="K103" s="1">
-        <v>100</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -24312,10 +24312,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J109">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -24379,10 +24379,10 @@
         <v>8.6</v>
       </c>
       <c r="J111">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="K111" s="1">
-        <v>31.8</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -24399,25 +24399,25 @@
         <v>33</v>
       </c>
       <c r="E112">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1">
+        <v>97</v>
+      </c>
+      <c r="H112" s="1">
         <v>3</v>
       </c>
-      <c r="G112" s="1">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="H112" s="1">
-        <v>9.1</v>
-      </c>
       <c r="I112" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J112">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -24434,25 +24434,25 @@
         <v>21</v>
       </c>
       <c r="E113">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G113" s="1">
-        <v>85.7</v>
+        <v>90.5</v>
       </c>
       <c r="H113" s="1">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="I113" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J113">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K113" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -24469,25 +24469,25 @@
         <v>25</v>
       </c>
       <c r="E114">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114" s="1">
+        <v>96</v>
+      </c>
+      <c r="H114" s="1">
         <v>4</v>
       </c>
-      <c r="G114" s="1">
-        <v>84</v>
-      </c>
-      <c r="H114" s="1">
-        <v>16</v>
-      </c>
       <c r="I114" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J114">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K114" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -24504,25 +24504,25 @@
         <v>19</v>
       </c>
       <c r="E115">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G115" s="1">
-        <v>84.2</v>
+        <v>94.7</v>
       </c>
       <c r="H115" s="1">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="I115" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J115">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K115" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -24571,25 +24571,25 @@
         <v>119</v>
       </c>
       <c r="E117">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F117">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G117" s="1">
-        <v>88.2</v>
+        <v>95</v>
       </c>
       <c r="H117" s="1">
-        <v>11.8</v>
+        <v>5</v>
       </c>
       <c r="I117" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J117">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>82.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -25239,13 +25239,13 @@
         <v>0</v>
       </c>
       <c r="I136" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J136">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K136" s="1">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -25309,13 +25309,13 @@
         <v>0</v>
       </c>
       <c r="I138" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J138">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K138" s="1">
-        <v>100</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -25332,25 +25332,25 @@
         <v>22</v>
       </c>
       <c r="E139">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139" s="1">
+        <v>95.5</v>
+      </c>
+      <c r="H139" s="1">
+        <v>0</v>
+      </c>
+      <c r="I139" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="J139">
         <v>1</v>
       </c>
-      <c r="G139" s="1">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="H139" s="1">
+      <c r="K139" s="1">
         <v>4.5</v>
-      </c>
-      <c r="I139" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J139">
-        <v>22</v>
-      </c>
-      <c r="K139" s="1">
-        <v>100</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -25367,25 +25367,25 @@
         <v>28</v>
       </c>
       <c r="E140">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F140">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G140" s="1">
-        <v>96.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H140" s="1">
-        <v>3.6</v>
+        <v>17.9</v>
       </c>
       <c r="I140" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J140">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K140" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -25399,25 +25399,25 @@
         <v>127</v>
       </c>
       <c r="E141">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F141">
+        <v>5</v>
+      </c>
+      <c r="G141" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="H141" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="I141" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="J141">
         <v>2</v>
       </c>
-      <c r="G141" s="1">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="H141" s="1">
+      <c r="K141" s="1">
         <v>1.6</v>
-      </c>
-      <c r="I141" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="J141">
-        <v>95</v>
-      </c>
-      <c r="K141" s="1">
-        <v>74.8</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -25641,25 +25641,25 @@
         <v>21</v>
       </c>
       <c r="E148">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F148">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G148" s="1">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H148" s="1">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="I148" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J148">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -25676,25 +25676,25 @@
         <v>19</v>
       </c>
       <c r="E149">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G149" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="H149" s="1">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="I149" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J149">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -25711,25 +25711,25 @@
         <v>21</v>
       </c>
       <c r="E150">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G150" s="1">
-        <v>90.5</v>
+        <v>95.2</v>
       </c>
       <c r="H150" s="1">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="I150" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J150">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -25746,25 +25746,25 @@
         <v>24</v>
       </c>
       <c r="E151">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F151">
         <v>0</v>
       </c>
       <c r="G151" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
       </c>
       <c r="I151" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J151">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -25778,25 +25778,25 @@
         <v>85</v>
       </c>
       <c r="E152">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F152">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G152" s="1">
-        <v>87.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H152" s="1">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="I152" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J152">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -26755,13 +26755,13 @@
         <v>20.8</v>
       </c>
       <c r="I180" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J180">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -26778,25 +26778,25 @@
         <v>36</v>
       </c>
       <c r="E181">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F181">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G181" s="1">
-        <v>88.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="H181" s="1">
-        <v>11.1</v>
+        <v>2.8</v>
       </c>
       <c r="I181" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J181">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -26813,25 +26813,25 @@
         <v>28</v>
       </c>
       <c r="E182">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G182" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H182" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I182" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J182">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K182" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -26848,25 +26848,25 @@
         <v>35</v>
       </c>
       <c r="E183">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F183">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H183" s="1">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="I183" s="2">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="J183">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -26883,25 +26883,25 @@
         <v>24</v>
       </c>
       <c r="E184">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F184">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>70.8</v>
+        <v>100</v>
       </c>
       <c r="H184" s="1">
-        <v>29.2</v>
+        <v>0</v>
       </c>
       <c r="I184" s="2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J184">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -26930,13 +26930,13 @@
         <v>2.7</v>
       </c>
       <c r="I185" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J185">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -26950,25 +26950,25 @@
         <v>184</v>
       </c>
       <c r="E186">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="F186">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G186" s="1">
-        <v>87.5</v>
+        <v>95.7</v>
       </c>
       <c r="H186" s="1">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="I186" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J186">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -28574,25 +28574,25 @@
         <v>28</v>
       </c>
       <c r="E233">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F233">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G233" s="1">
-        <v>75</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H233" s="1">
-        <v>25</v>
+        <v>17.9</v>
       </c>
       <c r="I233" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J233">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K233" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -28609,25 +28609,25 @@
         <v>18</v>
       </c>
       <c r="E234">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F234">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G234" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H234" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I234" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J234">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K234" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -28656,13 +28656,13 @@
         <v>0</v>
       </c>
       <c r="I235" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J235">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K235" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -28676,25 +28676,25 @@
         <v>91</v>
       </c>
       <c r="E236">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F236">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G236" s="1">
-        <v>82.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H236" s="1">
-        <v>15.4</v>
+        <v>9.9</v>
       </c>
       <c r="I236" s="2">
         <v>7</v>
       </c>
       <c r="J236">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="K236" s="1">
-        <v>78</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -29067,10 +29067,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J247">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K247" s="1">
-        <v>36.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -29099,10 +29099,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J248">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K248" s="1">
-        <v>36.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -29632,25 +29632,25 @@
         <v>40</v>
       </c>
       <c r="E264">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F264">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G264" s="1">
-        <v>45</v>
+        <v>72.5</v>
       </c>
       <c r="H264" s="1">
-        <v>55</v>
+        <v>27.5</v>
       </c>
       <c r="I264" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J264">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K264" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -29664,25 +29664,25 @@
         <v>40</v>
       </c>
       <c r="E265">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F265">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G265" s="1">
-        <v>45</v>
+        <v>72.5</v>
       </c>
       <c r="H265" s="1">
-        <v>55</v>
+        <v>27.5</v>
       </c>
       <c r="I265" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J265">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K265" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:11">
@@ -29976,25 +29976,25 @@
         <v>48</v>
       </c>
       <c r="E274">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F274">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G274" s="1">
-        <v>85.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="H274" s="1">
-        <v>14.6</v>
+        <v>4.2</v>
       </c>
       <c r="I274" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J274">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K274" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:11">
@@ -30058,13 +30058,13 @@
         <v>6.1</v>
       </c>
       <c r="I276" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J276">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K276" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:11">
@@ -30081,25 +30081,25 @@
         <v>35</v>
       </c>
       <c r="E277">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F277">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G277" s="1">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="H277" s="1">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I277" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J277">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K277" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:11">
@@ -30116,25 +30116,25 @@
         <v>24</v>
       </c>
       <c r="E278">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F278">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G278" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H278" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I278" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J278">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K278" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -30148,25 +30148,25 @@
         <v>258</v>
       </c>
       <c r="E279">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="F279">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G279" s="1">
-        <v>87.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H279" s="1">
-        <v>12.4</v>
+        <v>8.1</v>
       </c>
       <c r="I279" s="2">
         <v>7.9</v>
       </c>
       <c r="J279">
-        <v>258</v>
+        <v>118</v>
       </c>
       <c r="K279" s="1">
-        <v>100</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -30425,25 +30425,25 @@
         <v>22</v>
       </c>
       <c r="E287">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F287">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G287" s="1">
-        <v>68.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H287" s="1">
-        <v>31.8</v>
+        <v>13.6</v>
       </c>
       <c r="I287" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J287">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K287" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -30460,25 +30460,25 @@
         <v>29</v>
       </c>
       <c r="E288">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F288">
+        <v>0</v>
+      </c>
+      <c r="G288" s="1">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="H288" s="1">
+        <v>0</v>
+      </c>
+      <c r="I288" s="2">
+        <v>8</v>
+      </c>
+      <c r="J288">
         <v>1</v>
       </c>
-      <c r="G288" s="1">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="H288" s="1">
+      <c r="K288" s="1">
         <v>3.4</v>
-      </c>
-      <c r="I288" s="2">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J288">
-        <v>29</v>
-      </c>
-      <c r="K288" s="1">
-        <v>100</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -30495,25 +30495,25 @@
         <v>31</v>
       </c>
       <c r="E289">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F289">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G289" s="1">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="H289" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I289" s="2">
         <v>7.8</v>
       </c>
       <c r="J289">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K289" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -30597,25 +30597,25 @@
         <v>126</v>
       </c>
       <c r="E292">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F292">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G292" s="1">
-        <v>88.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="H292" s="1">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="I292" s="2">
         <v>7.6</v>
       </c>
       <c r="J292">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="K292" s="1">
-        <v>100</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="293" spans="1:11">

--- a/DetalleXDocente20241.xlsx
+++ b/DetalleXDocente20241.xlsx
@@ -22701,25 +22701,25 @@
         <v>23</v>
       </c>
       <c r="E55">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F55">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G55" s="1">
-        <v>52.2</v>
+        <v>65.2</v>
       </c>
       <c r="H55" s="1">
-        <v>47.8</v>
+        <v>34.8</v>
       </c>
       <c r="I55" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J55">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -22771,25 +22771,25 @@
         <v>21</v>
       </c>
       <c r="E57">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F57">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G57" s="1">
-        <v>47.6</v>
+        <v>61.9</v>
       </c>
       <c r="H57" s="1">
-        <v>52.4</v>
+        <v>38.1</v>
       </c>
       <c r="I57" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J57">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K57" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -22803,25 +22803,25 @@
         <v>170</v>
       </c>
       <c r="E58">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F58">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G58" s="1">
-        <v>72.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="H58" s="1">
-        <v>27.1</v>
+        <v>23.5</v>
       </c>
       <c r="I58" s="2">
         <v>6.4</v>
       </c>
       <c r="J58">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>25.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11">

--- a/DetalleXDocente20241.xlsx
+++ b/DetalleXDocente20241.xlsx
@@ -951,25 +951,25 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>79.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H5" s="1">
         <v>6.9</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1018,25 +1018,25 @@
         <v>120</v>
       </c>
       <c r="E7">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>92.5</v>
+        <v>95.8</v>
       </c>
       <c r="H7" s="1">
         <v>4.2</v>
       </c>
       <c r="I7" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1849,13 +1849,13 @@
         <v>24</v>
       </c>
       <c r="E31">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H31" s="1">
         <v>4.2</v>
@@ -1864,10 +1864,10 @@
         <v>9</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1881,13 +1881,13 @@
         <v>150</v>
       </c>
       <c r="E32">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F32">
         <v>20</v>
       </c>
       <c r="G32" s="1">
-        <v>86</v>
+        <v>86.7</v>
       </c>
       <c r="H32" s="1">
         <v>13.3</v>
@@ -1896,10 +1896,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1916,25 +1916,25 @@
         <v>29</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1948,25 +1948,25 @@
         <v>29</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
       <c r="I34" s="2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4092,25 +4092,25 @@
         <v>29</v>
       </c>
       <c r="E104">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F104">
         <v>5</v>
       </c>
       <c r="G104" s="1">
-        <v>79.3</v>
+        <v>82.8</v>
       </c>
       <c r="H104" s="1">
         <v>17.2</v>
       </c>
       <c r="I104" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4197,25 +4197,25 @@
         <v>44</v>
       </c>
       <c r="E107">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F107">
         <v>5</v>
       </c>
       <c r="G107" s="1">
-        <v>79.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H107" s="1">
         <v>11.4</v>
       </c>
       <c r="I107" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J107">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -4302,13 +4302,13 @@
         <v>24</v>
       </c>
       <c r="E110">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F110">
         <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -4317,10 +4317,10 @@
         <v>8.5</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4334,13 +4334,13 @@
         <v>239</v>
       </c>
       <c r="E111">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F111">
         <v>17</v>
       </c>
       <c r="G111" s="1">
-        <v>90.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H111" s="1">
         <v>7.1</v>
@@ -4349,10 +4349,10 @@
         <v>8.1</v>
       </c>
       <c r="J111">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4888,25 +4888,25 @@
         <v>29</v>
       </c>
       <c r="E127">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F127">
         <v>3</v>
       </c>
       <c r="G127" s="1">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="H127" s="1">
         <v>10.3</v>
       </c>
       <c r="I127" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5095,13 +5095,13 @@
         <v>260</v>
       </c>
       <c r="E133">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F133">
         <v>53</v>
       </c>
       <c r="G133" s="1">
-        <v>79.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H133" s="1">
         <v>20.4</v>
@@ -5110,10 +5110,10 @@
         <v>7.7</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5267,25 +5267,25 @@
         <v>29</v>
       </c>
       <c r="E138">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F138">
         <v>2</v>
       </c>
       <c r="G138" s="1">
-        <v>89.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H138" s="1">
         <v>6.9</v>
       </c>
       <c r="I138" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -5302,25 +5302,25 @@
         <v>22</v>
       </c>
       <c r="E139">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F139">
         <v>1</v>
       </c>
       <c r="G139" s="1">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="H139" s="1">
         <v>4.5</v>
       </c>
       <c r="I139" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -5369,13 +5369,13 @@
         <v>127</v>
       </c>
       <c r="E141">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F141">
         <v>8</v>
       </c>
       <c r="G141" s="1">
-        <v>92.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="H141" s="1">
         <v>6.3</v>
@@ -5384,10 +5384,10 @@
         <v>7.7</v>
       </c>
       <c r="J141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -5955,25 +5955,25 @@
         <v>29</v>
       </c>
       <c r="E158">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F158">
         <v>9</v>
       </c>
       <c r="G158" s="1">
-        <v>65.5</v>
+        <v>69</v>
       </c>
       <c r="H158" s="1">
         <v>31</v>
       </c>
       <c r="I158" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6060,25 +6060,25 @@
         <v>44</v>
       </c>
       <c r="E161">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F161">
         <v>13</v>
       </c>
       <c r="G161" s="1">
-        <v>61.4</v>
+        <v>70.5</v>
       </c>
       <c r="H161" s="1">
         <v>29.5</v>
       </c>
       <c r="I161" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J161">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -6162,13 +6162,13 @@
         <v>215</v>
       </c>
       <c r="E164">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F164">
         <v>51</v>
       </c>
       <c r="G164" s="1">
-        <v>74</v>
+        <v>76.3</v>
       </c>
       <c r="H164" s="1">
         <v>23.7</v>
@@ -6177,10 +6177,10 @@
         <v>6.9</v>
       </c>
       <c r="J164">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K164" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -6436,25 +6436,25 @@
         <v>21</v>
       </c>
       <c r="E172">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F172">
         <v>10</v>
       </c>
       <c r="G172" s="1">
-        <v>47.6</v>
+        <v>52.4</v>
       </c>
       <c r="H172" s="1">
         <v>47.6</v>
       </c>
       <c r="I172" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -6471,25 +6471,25 @@
         <v>21</v>
       </c>
       <c r="E173">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F173">
         <v>12</v>
       </c>
       <c r="G173" s="1">
-        <v>38.1</v>
+        <v>42.9</v>
       </c>
       <c r="H173" s="1">
         <v>57.1</v>
       </c>
       <c r="I173" s="2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -6576,13 +6576,13 @@
         <v>24</v>
       </c>
       <c r="E176">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F176">
         <v>0</v>
       </c>
       <c r="G176" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
@@ -6591,10 +6591,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -6611,25 +6611,25 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F177">
         <v>3</v>
       </c>
       <c r="G177" s="1">
-        <v>75.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="H177" s="1">
         <v>10.3</v>
       </c>
       <c r="I177" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J177">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -6646,25 +6646,25 @@
         <v>29</v>
       </c>
       <c r="E178">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F178">
         <v>9</v>
       </c>
       <c r="G178" s="1">
-        <v>55.2</v>
+        <v>69</v>
       </c>
       <c r="H178" s="1">
         <v>31</v>
       </c>
       <c r="I178" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J178">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K178" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -6678,25 +6678,25 @@
         <v>160</v>
       </c>
       <c r="E179">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F179">
         <v>49</v>
       </c>
       <c r="G179" s="1">
-        <v>62.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H179" s="1">
         <v>30.6</v>
       </c>
       <c r="I179" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J179">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>6.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -8407,13 +8407,13 @@
         <v>29</v>
       </c>
       <c r="E229">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F229">
         <v>4</v>
       </c>
       <c r="G229" s="1">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="H229" s="1">
         <v>13.8</v>
@@ -8422,10 +8422,10 @@
         <v>7.4</v>
       </c>
       <c r="J229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -8474,13 +8474,13 @@
         <v>101</v>
       </c>
       <c r="E231">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F231">
         <v>8</v>
       </c>
       <c r="G231" s="1">
-        <v>91.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H231" s="1">
         <v>7.9</v>
@@ -8489,10 +8489,10 @@
         <v>8.1</v>
       </c>
       <c r="J231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K231" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -8509,25 +8509,25 @@
         <v>21</v>
       </c>
       <c r="E232">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F232">
         <v>9</v>
       </c>
       <c r="G232" s="1">
-        <v>52.4</v>
+        <v>57.1</v>
       </c>
       <c r="H232" s="1">
         <v>42.9</v>
       </c>
       <c r="I232" s="2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K232" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -8614,25 +8614,25 @@
         <v>24</v>
       </c>
       <c r="E235">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F235">
         <v>1</v>
       </c>
       <c r="G235" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H235" s="1">
         <v>4.2</v>
       </c>
       <c r="I235" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -8646,25 +8646,25 @@
         <v>91</v>
       </c>
       <c r="E236">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F236">
         <v>23</v>
       </c>
       <c r="G236" s="1">
-        <v>72.5</v>
+        <v>74.7</v>
       </c>
       <c r="H236" s="1">
         <v>25.3</v>
       </c>
       <c r="I236" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K236" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -9022,25 +9022,25 @@
         <v>44</v>
       </c>
       <c r="E247">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F247">
         <v>0</v>
       </c>
       <c r="G247" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
       </c>
       <c r="I247" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J247">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K247" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -9054,25 +9054,25 @@
         <v>44</v>
       </c>
       <c r="E248">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F248">
         <v>0</v>
       </c>
       <c r="G248" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
       </c>
       <c r="I248" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J248">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K248" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -10430,25 +10430,25 @@
         <v>29</v>
       </c>
       <c r="E288">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F288">
         <v>1</v>
       </c>
       <c r="G288" s="1">
-        <v>93.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H288" s="1">
         <v>3.4</v>
       </c>
       <c r="I288" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K288" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -10500,25 +10500,25 @@
         <v>22</v>
       </c>
       <c r="E290">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F290">
         <v>0</v>
       </c>
       <c r="G290" s="1">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
       </c>
       <c r="I290" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K290" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -10535,25 +10535,25 @@
         <v>22</v>
       </c>
       <c r="E291">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F291">
         <v>2</v>
       </c>
       <c r="G291" s="1">
-        <v>86.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H291" s="1">
         <v>9.1</v>
       </c>
       <c r="I291" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J291">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K291" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -10567,13 +10567,13 @@
         <v>126</v>
       </c>
       <c r="E292">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F292">
         <v>17</v>
       </c>
       <c r="G292" s="1">
-        <v>84.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="H292" s="1">
         <v>13.5</v>
@@ -10582,10 +10582,10 @@
         <v>7.6</v>
       </c>
       <c r="J292">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K292" s="1">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -10966,25 +10966,25 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -11033,25 +11033,25 @@
         <v>120</v>
       </c>
       <c r="E7">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>94.2</v>
+        <v>97.5</v>
       </c>
       <c r="H7" s="1">
         <v>2.5</v>
       </c>
       <c r="I7" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -11864,25 +11864,25 @@
         <v>24</v>
       </c>
       <c r="E31">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H31" s="1">
         <v>4.2</v>
       </c>
       <c r="I31" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -11896,13 +11896,13 @@
         <v>150</v>
       </c>
       <c r="E32">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F32">
         <v>12</v>
       </c>
       <c r="G32" s="1">
-        <v>91.3</v>
+        <v>92</v>
       </c>
       <c r="H32" s="1">
         <v>8</v>
@@ -11911,10 +11911,10 @@
         <v>8</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -11931,13 +11931,13 @@
         <v>29</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -11946,10 +11946,10 @@
         <v>9.4</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -11963,13 +11963,13 @@
         <v>29</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -11978,10 +11978,10 @@
         <v>9.4</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -14107,13 +14107,13 @@
         <v>29</v>
       </c>
       <c r="E104">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -14122,10 +14122,10 @@
         <v>9</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -14212,13 +14212,13 @@
         <v>44</v>
       </c>
       <c r="E107">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F107">
         <v>0</v>
       </c>
       <c r="G107" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -14227,10 +14227,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J107">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -14317,13 +14317,13 @@
         <v>24</v>
       </c>
       <c r="E110">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F110">
         <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -14332,10 +14332,10 @@
         <v>9</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -14349,13 +14349,13 @@
         <v>239</v>
       </c>
       <c r="E111">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F111">
         <v>2</v>
       </c>
       <c r="G111" s="1">
-        <v>96.7</v>
+        <v>99.2</v>
       </c>
       <c r="H111" s="1">
         <v>0.8</v>
@@ -14364,10 +14364,10 @@
         <v>8.9</v>
       </c>
       <c r="J111">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -14903,13 +14903,13 @@
         <v>29</v>
       </c>
       <c r="E127">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F127">
         <v>3</v>
       </c>
       <c r="G127" s="1">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="H127" s="1">
         <v>10.3</v>
@@ -14918,10 +14918,10 @@
         <v>8.5</v>
       </c>
       <c r="J127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -15110,13 +15110,13 @@
         <v>260</v>
       </c>
       <c r="E133">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F133">
         <v>30</v>
       </c>
       <c r="G133" s="1">
-        <v>88.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="H133" s="1">
         <v>11.5</v>
@@ -15125,10 +15125,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -15282,25 +15282,25 @@
         <v>29</v>
       </c>
       <c r="E138">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F138">
         <v>0</v>
       </c>
       <c r="G138" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H138" s="1">
         <v>0</v>
       </c>
       <c r="I138" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -15317,25 +15317,25 @@
         <v>22</v>
       </c>
       <c r="E139">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F139">
         <v>1</v>
       </c>
       <c r="G139" s="1">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="H139" s="1">
         <v>4.5</v>
       </c>
       <c r="I139" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -15384,13 +15384,13 @@
         <v>127</v>
       </c>
       <c r="E141">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F141">
         <v>2</v>
       </c>
       <c r="G141" s="1">
-        <v>96.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H141" s="1">
         <v>1.6</v>
@@ -15399,10 +15399,10 @@
         <v>7.6</v>
       </c>
       <c r="J141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -15970,13 +15970,13 @@
         <v>29</v>
       </c>
       <c r="E158">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F158">
         <v>5</v>
       </c>
       <c r="G158" s="1">
-        <v>79.3</v>
+        <v>82.8</v>
       </c>
       <c r="H158" s="1">
         <v>17.2</v>
@@ -15985,10 +15985,10 @@
         <v>7.4</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -16075,25 +16075,25 @@
         <v>44</v>
       </c>
       <c r="E161">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F161">
         <v>8</v>
       </c>
       <c r="G161" s="1">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
       <c r="H161" s="1">
         <v>18.2</v>
       </c>
       <c r="I161" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J161">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -16177,13 +16177,13 @@
         <v>215</v>
       </c>
       <c r="E164">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F164">
         <v>23</v>
       </c>
       <c r="G164" s="1">
-        <v>87</v>
+        <v>89.3</v>
       </c>
       <c r="H164" s="1">
         <v>10.7</v>
@@ -16192,10 +16192,10 @@
         <v>8</v>
       </c>
       <c r="J164">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K164" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -16451,13 +16451,13 @@
         <v>21</v>
       </c>
       <c r="E172">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F172">
         <v>5</v>
       </c>
       <c r="G172" s="1">
-        <v>71.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="H172" s="1">
         <v>23.8</v>
@@ -16466,10 +16466,10 @@
         <v>7.5</v>
       </c>
       <c r="J172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -16486,25 +16486,25 @@
         <v>21</v>
       </c>
       <c r="E173">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F173">
         <v>8</v>
       </c>
       <c r="G173" s="1">
-        <v>57.1</v>
+        <v>61.9</v>
       </c>
       <c r="H173" s="1">
         <v>38.1</v>
       </c>
       <c r="I173" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -16591,25 +16591,25 @@
         <v>24</v>
       </c>
       <c r="E176">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F176">
         <v>0</v>
       </c>
       <c r="G176" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
       </c>
       <c r="I176" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -16626,25 +16626,25 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F177">
         <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
       </c>
       <c r="I177" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J177">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -16661,13 +16661,13 @@
         <v>29</v>
       </c>
       <c r="E178">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F178">
         <v>3</v>
       </c>
       <c r="G178" s="1">
-        <v>75.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="H178" s="1">
         <v>10.3</v>
@@ -16676,10 +16676,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J178">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K178" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -16693,25 +16693,25 @@
         <v>160</v>
       </c>
       <c r="E179">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F179">
         <v>26</v>
       </c>
       <c r="G179" s="1">
-        <v>76.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="H179" s="1">
         <v>16.2</v>
       </c>
       <c r="I179" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J179">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>6.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -18422,25 +18422,25 @@
         <v>29</v>
       </c>
       <c r="E229">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F229">
         <v>4</v>
       </c>
       <c r="G229" s="1">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="H229" s="1">
         <v>13.8</v>
       </c>
       <c r="I229" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -18489,13 +18489,13 @@
         <v>101</v>
       </c>
       <c r="E231">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F231">
         <v>7</v>
       </c>
       <c r="G231" s="1">
-        <v>92.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H231" s="1">
         <v>6.9</v>
@@ -18504,10 +18504,10 @@
         <v>8</v>
       </c>
       <c r="J231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K231" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -18524,25 +18524,25 @@
         <v>21</v>
       </c>
       <c r="E232">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F232">
         <v>11</v>
       </c>
       <c r="G232" s="1">
-        <v>42.9</v>
+        <v>47.6</v>
       </c>
       <c r="H232" s="1">
         <v>52.4</v>
       </c>
       <c r="I232" s="2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K232" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -18629,25 +18629,25 @@
         <v>24</v>
       </c>
       <c r="E235">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F235">
         <v>0</v>
       </c>
       <c r="G235" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
       </c>
       <c r="I235" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -18661,13 +18661,13 @@
         <v>91</v>
       </c>
       <c r="E236">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F236">
         <v>21</v>
       </c>
       <c r="G236" s="1">
-        <v>74.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H236" s="1">
         <v>23.1</v>
@@ -18676,10 +18676,10 @@
         <v>7</v>
       </c>
       <c r="J236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K236" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -19037,25 +19037,25 @@
         <v>44</v>
       </c>
       <c r="E247">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F247">
         <v>0</v>
       </c>
       <c r="G247" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
       </c>
       <c r="I247" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J247">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K247" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -19069,25 +19069,25 @@
         <v>44</v>
       </c>
       <c r="E248">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F248">
         <v>0</v>
       </c>
       <c r="G248" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
       </c>
       <c r="I248" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J248">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K248" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -20445,25 +20445,25 @@
         <v>29</v>
       </c>
       <c r="E288">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F288">
         <v>1</v>
       </c>
       <c r="G288" s="1">
-        <v>93.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H288" s="1">
         <v>3.4</v>
       </c>
       <c r="I288" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K288" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -20515,25 +20515,25 @@
         <v>22</v>
       </c>
       <c r="E290">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F290">
         <v>0</v>
       </c>
       <c r="G290" s="1">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
       </c>
       <c r="I290" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K290" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -20550,25 +20550,25 @@
         <v>22</v>
       </c>
       <c r="E291">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F291">
         <v>2</v>
       </c>
       <c r="G291" s="1">
-        <v>86.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H291" s="1">
         <v>9.1</v>
       </c>
       <c r="I291" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J291">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K291" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -20582,25 +20582,25 @@
         <v>126</v>
       </c>
       <c r="E292">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F292">
         <v>12</v>
       </c>
       <c r="G292" s="1">
-        <v>88.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="H292" s="1">
         <v>9.5</v>
       </c>
       <c r="I292" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J292">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K292" s="1">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -20981,25 +20981,25 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -21048,13 +21048,13 @@
         <v>120</v>
       </c>
       <c r="E7">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -21063,10 +21063,10 @@
         <v>8.9</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -21879,13 +21879,13 @@
         <v>24</v>
       </c>
       <c r="E31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -21894,10 +21894,10 @@
         <v>9</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -21911,13 +21911,13 @@
         <v>150</v>
       </c>
       <c r="E32">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F32">
         <v>6</v>
       </c>
       <c r="G32" s="1">
-        <v>95.3</v>
+        <v>96</v>
       </c>
       <c r="H32" s="1">
         <v>4</v>
@@ -21926,10 +21926,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -21946,25 +21946,25 @@
         <v>29</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -21978,25 +21978,25 @@
         <v>29</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
       <c r="I34" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -22494,25 +22494,25 @@
         <v>41</v>
       </c>
       <c r="E49">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>95.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H49" s="1">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="I49" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J49">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -22529,25 +22529,25 @@
         <v>34</v>
       </c>
       <c r="E50">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" s="1">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H50" s="1">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="I50" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J50">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -22561,25 +22561,25 @@
         <v>75</v>
       </c>
       <c r="E51">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G51" s="1">
-        <v>94.7</v>
+        <v>97.3</v>
       </c>
       <c r="H51" s="1">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="I51" s="2">
         <v>8.6</v>
       </c>
       <c r="J51">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -23778,25 +23778,25 @@
         <v>18</v>
       </c>
       <c r="E94">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F94">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="H94" s="1">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="I94" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J94">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -23813,25 +23813,25 @@
         <v>24</v>
       </c>
       <c r="E95">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F95">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H95" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I95" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J95">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K95" s="1">
-        <v>95.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -23845,25 +23845,25 @@
         <v>109</v>
       </c>
       <c r="E96">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F96">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G96" s="1">
-        <v>87.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H96" s="1">
-        <v>12.8</v>
+        <v>4.6</v>
       </c>
       <c r="I96" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J96">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K96" s="1">
-        <v>37.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -23985,25 +23985,25 @@
         <v>36</v>
       </c>
       <c r="E100">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G100" s="1">
-        <v>94.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="H100" s="1">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="I100" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J100">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K100" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -24020,25 +24020,25 @@
         <v>37</v>
       </c>
       <c r="E101">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G101" s="1">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H101" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I101" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J101">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -24087,25 +24087,25 @@
         <v>235</v>
       </c>
       <c r="E103">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F103">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G103" s="1">
-        <v>96.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H103" s="1">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="I103" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J103">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>31.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -24122,25 +24122,25 @@
         <v>29</v>
       </c>
       <c r="E104">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -24207,10 +24207,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J106">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -24227,25 +24227,25 @@
         <v>44</v>
       </c>
       <c r="E107">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F107">
         <v>2</v>
       </c>
       <c r="G107" s="1">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="H107" s="1">
         <v>4.5</v>
       </c>
       <c r="I107" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J107">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -24332,13 +24332,13 @@
         <v>24</v>
       </c>
       <c r="E110">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F110">
         <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -24347,10 +24347,10 @@
         <v>8.9</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -24364,13 +24364,13 @@
         <v>239</v>
       </c>
       <c r="E111">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F111">
         <v>4</v>
       </c>
       <c r="G111" s="1">
-        <v>95.8</v>
+        <v>98.3</v>
       </c>
       <c r="H111" s="1">
         <v>1.7</v>
@@ -24379,10 +24379,10 @@
         <v>8.6</v>
       </c>
       <c r="J111">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -24606,25 +24606,25 @@
         <v>40</v>
       </c>
       <c r="E118">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F118">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G118" s="1">
-        <v>82.5</v>
+        <v>97.5</v>
       </c>
       <c r="H118" s="1">
-        <v>17.5</v>
+        <v>2.5</v>
       </c>
       <c r="I118" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J118">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K118" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -24641,25 +24641,25 @@
         <v>41</v>
       </c>
       <c r="E119">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F119">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G119" s="1">
-        <v>75.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="H119" s="1">
-        <v>24.4</v>
+        <v>7.3</v>
       </c>
       <c r="I119" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J119">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -24676,25 +24676,25 @@
         <v>48</v>
       </c>
       <c r="E120">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F120">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>79.2</v>
+        <v>100</v>
       </c>
       <c r="H120" s="1">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="I120" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J120">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K120" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -24711,25 +24711,25 @@
         <v>36</v>
       </c>
       <c r="E121">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121" s="1">
+        <v>97.2</v>
+      </c>
+      <c r="H121" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="I121" s="2">
         <v>7</v>
       </c>
-      <c r="G121" s="1">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="H121" s="1">
-        <v>19.4</v>
-      </c>
-      <c r="I121" s="2">
-        <v>6.6</v>
-      </c>
       <c r="J121">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K121" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -24746,25 +24746,25 @@
         <v>37</v>
       </c>
       <c r="E122">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F122">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G122" s="1">
-        <v>73</v>
+        <v>97.3</v>
       </c>
       <c r="H122" s="1">
-        <v>27</v>
+        <v>2.7</v>
       </c>
       <c r="I122" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J122">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -24781,25 +24781,25 @@
         <v>33</v>
       </c>
       <c r="E123">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F123">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G123" s="1">
-        <v>78.8</v>
+        <v>97</v>
       </c>
       <c r="H123" s="1">
-        <v>21.2</v>
+        <v>3</v>
       </c>
       <c r="I123" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J123">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K123" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -24813,25 +24813,25 @@
         <v>235</v>
       </c>
       <c r="E124">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="F124">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G124" s="1">
-        <v>78.3</v>
+        <v>97</v>
       </c>
       <c r="H124" s="1">
-        <v>21.7</v>
+        <v>3</v>
       </c>
       <c r="I124" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J124">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -24848,25 +24848,25 @@
         <v>40</v>
       </c>
       <c r="E125">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F125">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G125" s="1">
-        <v>75</v>
+        <v>92.5</v>
       </c>
       <c r="H125" s="1">
-        <v>25</v>
+        <v>7.5</v>
       </c>
       <c r="I125" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J125">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -24883,25 +24883,25 @@
         <v>41</v>
       </c>
       <c r="E126">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F126">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G126" s="1">
-        <v>82.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="H126" s="1">
-        <v>17.1</v>
+        <v>7.3</v>
       </c>
       <c r="I126" s="2">
         <v>7.6</v>
       </c>
       <c r="J126">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -24918,25 +24918,25 @@
         <v>29</v>
       </c>
       <c r="E127">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F127">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G127" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H127" s="1">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="I127" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J127">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -24953,25 +24953,25 @@
         <v>29</v>
       </c>
       <c r="E128">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H128" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I128" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J128">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>96.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -24988,25 +24988,25 @@
         <v>31</v>
       </c>
       <c r="E129">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H129" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I129" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J129">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -25023,25 +25023,25 @@
         <v>31</v>
       </c>
       <c r="E130">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G130" s="1">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="H130" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I130" s="2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J130">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -25058,25 +25058,25 @@
         <v>31</v>
       </c>
       <c r="E131">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131" s="1">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="H131" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I131" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J131">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -25093,25 +25093,25 @@
         <v>28</v>
       </c>
       <c r="E132">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F132">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G132" s="1">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="H132" s="1">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="I132" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J132">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -25125,25 +25125,25 @@
         <v>260</v>
       </c>
       <c r="E133">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F133">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G133" s="1">
-        <v>88.09999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="H133" s="1">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="I133" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J133">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>99.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -25160,25 +25160,25 @@
         <v>41</v>
       </c>
       <c r="E134">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F134">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G134" s="1">
-        <v>90.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H134" s="1">
-        <v>9.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="I134" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J134">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K134" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -25192,25 +25192,25 @@
         <v>41</v>
       </c>
       <c r="E135">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F135">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G135" s="1">
-        <v>90.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H135" s="1">
-        <v>9.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="I135" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J135">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K135" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -25297,13 +25297,13 @@
         <v>29</v>
       </c>
       <c r="E138">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F138">
         <v>0</v>
       </c>
       <c r="G138" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H138" s="1">
         <v>0</v>
@@ -25312,10 +25312,10 @@
         <v>8</v>
       </c>
       <c r="J138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -25332,25 +25332,25 @@
         <v>22</v>
       </c>
       <c r="E139">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F139">
         <v>0</v>
       </c>
       <c r="G139" s="1">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
       </c>
       <c r="I139" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -25399,13 +25399,13 @@
         <v>127</v>
       </c>
       <c r="E141">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F141">
         <v>5</v>
       </c>
       <c r="G141" s="1">
-        <v>94.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H141" s="1">
         <v>3.9</v>
@@ -25414,10 +25414,10 @@
         <v>7.8</v>
       </c>
       <c r="J141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -25449,10 +25449,10 @@
         <v>9</v>
       </c>
       <c r="J142">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -25481,13 +25481,13 @@
         <v>4.8</v>
       </c>
       <c r="I143" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J143">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -25504,25 +25504,25 @@
         <v>25</v>
       </c>
       <c r="E144">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G144" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H144" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I144" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J144">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -25539,25 +25539,25 @@
         <v>21</v>
       </c>
       <c r="E145">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G145" s="1">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="H145" s="1">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I145" s="2">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="J145">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -25586,13 +25586,13 @@
         <v>0</v>
       </c>
       <c r="I146" s="2">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J146">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K146" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -25606,25 +25606,25 @@
         <v>105</v>
       </c>
       <c r="E147">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F147">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G147" s="1">
-        <v>96.2</v>
+        <v>95.2</v>
       </c>
       <c r="H147" s="1">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="I147" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J147">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="K147" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -25985,25 +25985,25 @@
         <v>29</v>
       </c>
       <c r="E158">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F158">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G158" s="1">
-        <v>79.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H158" s="1">
-        <v>17.2</v>
+        <v>6.9</v>
       </c>
       <c r="I158" s="2">
         <v>7.4</v>
       </c>
       <c r="J158">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -26020,25 +26020,25 @@
         <v>41</v>
       </c>
       <c r="E159">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G159" s="1">
-        <v>92.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H159" s="1">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="I159" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J159">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K159" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -26055,25 +26055,25 @@
         <v>34</v>
       </c>
       <c r="E160">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G160" s="1">
-        <v>91.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H160" s="1">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="I160" s="2">
         <v>7.6</v>
       </c>
       <c r="J160">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -26090,25 +26090,25 @@
         <v>44</v>
       </c>
       <c r="E161">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F161">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G161" s="1">
-        <v>72.7</v>
+        <v>77.3</v>
       </c>
       <c r="H161" s="1">
-        <v>18.2</v>
+        <v>22.7</v>
       </c>
       <c r="I161" s="2">
         <v>7.3</v>
       </c>
       <c r="J161">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -26125,25 +26125,25 @@
         <v>31</v>
       </c>
       <c r="E162">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G162" s="1">
-        <v>87.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="H162" s="1">
-        <v>12.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I162" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J162">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -26172,13 +26172,13 @@
         <v>0</v>
       </c>
       <c r="I163" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J163">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K163" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -26192,25 +26192,25 @@
         <v>215</v>
       </c>
       <c r="E164">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F164">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G164" s="1">
-        <v>87</v>
+        <v>91.2</v>
       </c>
       <c r="H164" s="1">
-        <v>10.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I164" s="2">
         <v>7.6</v>
       </c>
       <c r="J164">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="K164" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -26411,13 +26411,13 @@
         <v>0</v>
       </c>
       <c r="I170" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J170">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -26443,13 +26443,13 @@
         <v>0</v>
       </c>
       <c r="I171" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J171">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K171" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -26466,25 +26466,25 @@
         <v>21</v>
       </c>
       <c r="E172">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F172">
         <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
       </c>
       <c r="I172" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -26501,25 +26501,25 @@
         <v>21</v>
       </c>
       <c r="E173">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F173">
         <v>0</v>
       </c>
       <c r="G173" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H173" s="1">
         <v>0</v>
       </c>
       <c r="I173" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -26606,13 +26606,13 @@
         <v>24</v>
       </c>
       <c r="E176">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F176">
         <v>0</v>
       </c>
       <c r="G176" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
@@ -26621,10 +26621,10 @@
         <v>8.5</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -26641,25 +26641,25 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F177">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H177" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I177" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J177">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -26676,25 +26676,25 @@
         <v>29</v>
       </c>
       <c r="E178">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F178">
         <v>0</v>
       </c>
       <c r="G178" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
       </c>
       <c r="I178" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J178">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K178" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -26708,25 +26708,25 @@
         <v>160</v>
       </c>
       <c r="E179">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="F179">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H179" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I179" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J179">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>6.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -27828,13 +27828,13 @@
         <v>21.2</v>
       </c>
       <c r="I211" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J211">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K211" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -27851,25 +27851,25 @@
         <v>41</v>
       </c>
       <c r="E212">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G212" s="1">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H212" s="1">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I212" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J212">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K212" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:11">
@@ -27886,25 +27886,25 @@
         <v>44</v>
       </c>
       <c r="E213">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G213" s="1">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="H213" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I213" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J213">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K213" s="1">
-        <v>90.90000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -27956,25 +27956,25 @@
         <v>21</v>
       </c>
       <c r="E215">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H215" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I215" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J215">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K215" s="1">
-        <v>95.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -28003,13 +28003,13 @@
         <v>0</v>
       </c>
       <c r="I216" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J216">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K216" s="1">
-        <v>86.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -28023,25 +28023,25 @@
         <v>204</v>
       </c>
       <c r="E217">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F217">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G217" s="1">
-        <v>95.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H217" s="1">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I217" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J217">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="K217" s="1">
-        <v>77.90000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -28367,25 +28367,25 @@
         <v>28</v>
       </c>
       <c r="E227">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G227" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H227" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I227" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J227">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K227" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -28417,10 +28417,10 @@
         <v>9</v>
       </c>
       <c r="J228">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K228" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -28437,25 +28437,25 @@
         <v>29</v>
       </c>
       <c r="E229">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F229">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G229" s="1">
-        <v>82.8</v>
+        <v>100</v>
       </c>
       <c r="H229" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I229" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J229">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K229" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -28472,25 +28472,25 @@
         <v>34</v>
       </c>
       <c r="E230">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G230" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H230" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I230" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J230">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K230" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -28504,25 +28504,25 @@
         <v>101</v>
       </c>
       <c r="E231">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F231">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G231" s="1">
-        <v>92.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="H231" s="1">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="I231" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J231">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K231" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -28539,25 +28539,25 @@
         <v>21</v>
       </c>
       <c r="E232">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F232">
         <v>4</v>
       </c>
       <c r="G232" s="1">
-        <v>76.2</v>
+        <v>81</v>
       </c>
       <c r="H232" s="1">
         <v>19</v>
       </c>
       <c r="I232" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K232" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -28644,25 +28644,25 @@
         <v>24</v>
       </c>
       <c r="E235">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F235">
         <v>0</v>
       </c>
       <c r="G235" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
       </c>
       <c r="I235" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -28676,13 +28676,13 @@
         <v>91</v>
       </c>
       <c r="E236">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F236">
         <v>9</v>
       </c>
       <c r="G236" s="1">
-        <v>87.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H236" s="1">
         <v>9.9</v>
@@ -28691,10 +28691,10 @@
         <v>7</v>
       </c>
       <c r="J236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K236" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -28711,25 +28711,25 @@
         <v>48</v>
       </c>
       <c r="E237">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F237">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G237" s="1">
-        <v>83.3</v>
+        <v>95.8</v>
       </c>
       <c r="H237" s="1">
-        <v>16.7</v>
+        <v>4.2</v>
       </c>
       <c r="I237" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J237">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K237" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -28746,25 +28746,25 @@
         <v>36</v>
       </c>
       <c r="E238">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F238">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G238" s="1">
-        <v>91.7</v>
+        <v>97.2</v>
       </c>
       <c r="H238" s="1">
-        <v>8.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I238" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J238">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K238" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -28781,25 +28781,25 @@
         <v>37</v>
       </c>
       <c r="E239">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F239">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G239" s="1">
-        <v>83.8</v>
+        <v>100</v>
       </c>
       <c r="H239" s="1">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="I239" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J239">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K239" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -28816,25 +28816,25 @@
         <v>33</v>
       </c>
       <c r="E240">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F240">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G240" s="1">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H240" s="1">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="I240" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J240">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K240" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -28851,25 +28851,25 @@
         <v>34</v>
       </c>
       <c r="E241">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F241">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G241" s="1">
-        <v>79.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H241" s="1">
-        <v>20.6</v>
+        <v>2.9</v>
       </c>
       <c r="I241" s="2">
         <v>7.1</v>
       </c>
       <c r="J241">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K241" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -28883,25 +28883,25 @@
         <v>188</v>
       </c>
       <c r="E242">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="F242">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G242" s="1">
-        <v>85.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="H242" s="1">
-        <v>14.4</v>
+        <v>3.2</v>
       </c>
       <c r="I242" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J242">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="K242" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -28918,25 +28918,25 @@
         <v>36</v>
       </c>
       <c r="E243">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F243">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G243" s="1">
-        <v>86.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H243" s="1">
-        <v>13.9</v>
+        <v>5.6</v>
       </c>
       <c r="I243" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J243">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K243" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -28950,25 +28950,25 @@
         <v>36</v>
       </c>
       <c r="E244">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F244">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G244" s="1">
-        <v>86.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H244" s="1">
-        <v>13.9</v>
+        <v>5.6</v>
       </c>
       <c r="I244" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J244">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K244" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -29052,25 +29052,25 @@
         <v>44</v>
       </c>
       <c r="E247">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F247">
         <v>0</v>
       </c>
       <c r="G247" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
       </c>
       <c r="I247" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J247">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K247" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -29084,25 +29084,25 @@
         <v>44</v>
       </c>
       <c r="E248">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F248">
         <v>0</v>
       </c>
       <c r="G248" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
       </c>
       <c r="I248" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J248">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K248" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -29119,25 +29119,25 @@
         <v>40</v>
       </c>
       <c r="E249">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F249">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G249" s="1">
-        <v>60</v>
+        <v>72.5</v>
       </c>
       <c r="H249" s="1">
-        <v>40</v>
+        <v>27.5</v>
       </c>
       <c r="I249" s="2">
         <v>6.3</v>
       </c>
       <c r="J249">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K249" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -29154,25 +29154,25 @@
         <v>34</v>
       </c>
       <c r="E250">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F250">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G250" s="1">
-        <v>38.2</v>
+        <v>52.9</v>
       </c>
       <c r="H250" s="1">
-        <v>61.8</v>
+        <v>47.1</v>
       </c>
       <c r="I250" s="2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J250">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K250" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -29189,25 +29189,25 @@
         <v>33</v>
       </c>
       <c r="E251">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F251">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G251" s="1">
-        <v>63.6</v>
+        <v>75.8</v>
       </c>
       <c r="H251" s="1">
-        <v>36.4</v>
+        <v>24.2</v>
       </c>
       <c r="I251" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J251">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K251" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -29236,13 +29236,13 @@
         <v>52.2</v>
       </c>
       <c r="I252" s="2">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="J252">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K252" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -29259,25 +29259,25 @@
         <v>19</v>
       </c>
       <c r="E253">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F253">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G253" s="1">
-        <v>84.2</v>
+        <v>94.7</v>
       </c>
       <c r="H253" s="1">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="I253" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J253">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K253" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -29294,25 +29294,25 @@
         <v>22</v>
       </c>
       <c r="E254">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F254">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G254" s="1">
-        <v>68.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H254" s="1">
-        <v>31.8</v>
+        <v>9.1</v>
       </c>
       <c r="I254" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J254">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K254" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -29326,25 +29326,25 @@
         <v>171</v>
       </c>
       <c r="E255">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F255">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G255" s="1">
-        <v>58.5</v>
+        <v>70.8</v>
       </c>
       <c r="H255" s="1">
-        <v>41.5</v>
+        <v>29.2</v>
       </c>
       <c r="I255" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J255">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="K255" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -29699,25 +29699,25 @@
         <v>40</v>
       </c>
       <c r="E266">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F266">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G266" s="1">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H266" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I266" s="2">
         <v>7.8</v>
       </c>
       <c r="J266">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K266" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -29734,25 +29734,25 @@
         <v>41</v>
       </c>
       <c r="E267">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F267">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G267" s="1">
-        <v>85.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="H267" s="1">
-        <v>14.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I267" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J267">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K267" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -29769,25 +29769,25 @@
         <v>48</v>
       </c>
       <c r="E268">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F268">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G268" s="1">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="H268" s="1">
-        <v>6.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I268" s="2">
         <v>7.9</v>
       </c>
       <c r="J268">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K268" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -29804,25 +29804,25 @@
         <v>36</v>
       </c>
       <c r="E269">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G269" s="1">
-        <v>94.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="H269" s="1">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="I269" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J269">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K269" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -29839,25 +29839,25 @@
         <v>37</v>
       </c>
       <c r="E270">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F270">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G270" s="1">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H270" s="1">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I270" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J270">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K270" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -29871,25 +29871,25 @@
         <v>202</v>
       </c>
       <c r="E271">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F271">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G271" s="1">
-        <v>91.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H271" s="1">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="I271" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J271">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="K271" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:11">
@@ -29906,25 +29906,25 @@
         <v>40</v>
       </c>
       <c r="E272">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F272">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G272" s="1">
-        <v>82.5</v>
+        <v>95</v>
       </c>
       <c r="H272" s="1">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="I272" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J272">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K272" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273" spans="1:11">
@@ -29941,25 +29941,25 @@
         <v>41</v>
       </c>
       <c r="E273">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F273">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G273" s="1">
-        <v>87.8</v>
+        <v>92.7</v>
       </c>
       <c r="H273" s="1">
-        <v>12.2</v>
+        <v>7.3</v>
       </c>
       <c r="I273" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J273">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K273" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274" spans="1:11">
@@ -30011,25 +30011,25 @@
         <v>37</v>
       </c>
       <c r="E275">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F275">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G275" s="1">
-        <v>86.5</v>
+        <v>100</v>
       </c>
       <c r="H275" s="1">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="I275" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J275">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K275" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:11">
@@ -30148,25 +30148,25 @@
         <v>258</v>
       </c>
       <c r="E279">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="F279">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G279" s="1">
-        <v>91.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="H279" s="1">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
       <c r="I279" s="2">
         <v>7.9</v>
       </c>
       <c r="J279">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="K279" s="1">
-        <v>45.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -30460,25 +30460,25 @@
         <v>29</v>
       </c>
       <c r="E288">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F288">
         <v>0</v>
       </c>
       <c r="G288" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H288" s="1">
         <v>0</v>
       </c>
       <c r="I288" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K288" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -30530,13 +30530,13 @@
         <v>22</v>
       </c>
       <c r="E290">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F290">
         <v>0</v>
       </c>
       <c r="G290" s="1">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -30545,10 +30545,10 @@
         <v>7.8</v>
       </c>
       <c r="J290">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K290" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -30565,25 +30565,25 @@
         <v>22</v>
       </c>
       <c r="E291">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F291">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G291" s="1">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H291" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I291" s="2">
         <v>7.7</v>
       </c>
       <c r="J291">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K291" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -30597,25 +30597,25 @@
         <v>126</v>
       </c>
       <c r="E292">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F292">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G292" s="1">
-        <v>93.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H292" s="1">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="I292" s="2">
         <v>7.6</v>
       </c>
       <c r="J292">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K292" s="1">
-        <v>35.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:11">
